--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="185">
   <si>
     <t>Materia</t>
   </si>
@@ -221,16 +221,16 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
+    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>NC</t>
@@ -1058,7 +1058,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>-1</v>
@@ -1067,13 +1067,13 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>-1</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1112,7 +1112,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1121,13 +1121,13 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>-1</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1144,13 +1144,13 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>-1</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1198,13 +1198,13 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1212,7 +1212,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>-1</v>
@@ -1221,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>-1</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1275,7 +1275,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1289,7 +1289,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>-1</v>
@@ -1298,13 +1298,13 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1352,13 +1352,13 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1366,7 +1366,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1375,13 +1375,13 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>-1</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1420,7 +1420,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1429,13 +1429,13 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1443,7 +1443,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1452,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1497,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1506,7 +1506,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>-1</v>
@@ -1520,7 +1520,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1529,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1583,7 +1583,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1597,7 +1597,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>-1</v>
@@ -1606,13 +1606,13 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>-1</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1651,7 +1651,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1660,13 +1660,13 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>-1</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1683,13 +1683,13 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>-1</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1737,13 +1737,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>-1</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1760,13 +1760,13 @@
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>-1</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1814,13 +1814,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1837,13 +1837,13 @@
         <v>9</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>-1</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1905,7 +1905,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>-1</v>
@@ -1914,13 +1914,13 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>-1</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1968,13 +1968,13 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>-1</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1982,7 +1982,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>-1</v>
@@ -1991,7 +1991,7 @@
         <v>8</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2045,7 +2045,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -2059,7 +2059,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>-1</v>
@@ -2068,13 +2068,13 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F17">
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2122,13 +2122,13 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2136,7 +2136,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>-1</v>
@@ -2145,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>-1</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2199,13 +2199,13 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>-1</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2213,7 +2213,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2222,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2290,7 +2290,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>-1</v>
@@ -2299,13 +2299,13 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2344,7 +2344,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2353,13 +2353,13 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2367,7 +2367,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>-1</v>
@@ -2376,7 +2376,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>-1</v>
@@ -2421,7 +2421,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>-1</v>
@@ -2453,13 +2453,13 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2530,7 +2530,7 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
         <v>-1</v>
@@ -2584,7 +2584,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2598,7 +2598,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>-1</v>
@@ -2607,13 +2607,13 @@
         <v>10</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>-1</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2652,7 +2652,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2661,13 +2661,13 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>-1</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2675,7 +2675,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>-1</v>
@@ -2684,13 +2684,13 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <v>-1</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2729,7 +2729,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2738,13 +2738,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>-1</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2752,7 +2752,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>-1</v>
@@ -2761,13 +2761,13 @@
         <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F26">
         <v>-1</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2815,13 +2815,13 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2829,7 +2829,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>-1</v>
@@ -2838,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -2883,7 +2883,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2892,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>-1</v>
@@ -2906,7 +2906,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>-1</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>-1</v>
@@ -2960,7 +2960,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2969,7 +2969,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -2983,7 +2983,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C29">
         <v>-1</v>
@@ -2992,7 +2992,7 @@
         <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F29">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>-1</v>
@@ -3060,7 +3060,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>-1</v>
@@ -3069,13 +3069,13 @@
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F30">
         <v>-1</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3123,13 +3123,13 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>-1</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3137,7 +3137,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>-1</v>
@@ -3146,13 +3146,13 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>-1</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3200,13 +3200,13 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>-1</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3214,7 +3214,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>-1</v>
@@ -3223,13 +3223,13 @@
         <v>9</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3268,7 +3268,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3277,13 +3277,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3291,7 +3291,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -3300,13 +3300,13 @@
         <v>9</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3354,13 +3354,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>-1</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3368,7 +3368,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>-1</v>
@@ -3377,13 +3377,13 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F34">
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3422,7 +3422,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3431,13 +3431,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>-1</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3445,7 +3445,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3454,13 +3454,13 @@
         <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F35">
         <v>-1</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3508,13 +3508,13 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>-1</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3522,7 +3522,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C36">
         <v>-1</v>
@@ -3531,13 +3531,13 @@
         <v>10</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3576,7 +3576,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3585,13 +3585,13 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>-1</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3599,7 +3599,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -3608,13 +3608,13 @@
         <v>9</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F37">
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3653,7 +3653,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3662,13 +3662,13 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>-1</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3676,7 +3676,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C38">
         <v>-1</v>
@@ -3685,7 +3685,7 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F38">
         <v>-1</v>
@@ -3730,7 +3730,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3739,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>-1</v>
@@ -3753,7 +3753,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C39">
         <v>-1</v>
@@ -3762,13 +3762,13 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3807,7 +3807,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -3816,13 +3816,13 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>-1</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3830,7 +3830,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>-1</v>
@@ -3839,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F40">
         <v>-1</v>
@@ -3884,7 +3884,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -3893,7 +3893,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X40">
         <v>-1</v>
@@ -3907,7 +3907,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C41">
         <v>-1</v>
@@ -3916,13 +3916,13 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F41">
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H41">
         <v>-1</v>
@@ -3961,7 +3961,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -3970,13 +3970,13 @@
         <v>9</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>-1</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3984,7 +3984,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>-1</v>
@@ -3993,7 +3993,7 @@
         <v>8</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F42">
         <v>-1</v>
@@ -4038,7 +4038,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U42">
         <v>-1</v>
@@ -4047,7 +4047,7 @@
         <v>8</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>-1</v>
@@ -4061,7 +4061,7 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>-1</v>
@@ -4070,13 +4070,13 @@
         <v>10</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F43">
         <v>-1</v>
       </c>
       <c r="G43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H43">
         <v>-1</v>
@@ -4115,7 +4115,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -4124,13 +4124,13 @@
         <v>10</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>-1</v>
       </c>
       <c r="Y43">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4138,7 +4138,7 @@
         <v>52</v>
       </c>
       <c r="B44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C44">
         <v>-1</v>
@@ -4147,13 +4147,13 @@
         <v>10</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F44">
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H44">
         <v>-1</v>
@@ -4192,7 +4192,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>-1</v>
@@ -4201,13 +4201,13 @@
         <v>10</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X44">
         <v>-1</v>
       </c>
       <c r="Y44">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4224,7 +4224,7 @@
         <v>7</v>
       </c>
       <c r="E45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F45">
         <v>-1</v>
@@ -4278,7 +4278,7 @@
         <v>7</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X45">
         <v>-1</v>
@@ -4292,7 +4292,7 @@
         <v>54</v>
       </c>
       <c r="B46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C46">
         <v>-1</v>
@@ -4301,13 +4301,13 @@
         <v>9</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F46">
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H46">
         <v>-1</v>
@@ -4346,7 +4346,7 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U46">
         <v>-1</v>
@@ -4355,13 +4355,13 @@
         <v>9</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X46">
         <v>-1</v>
       </c>
       <c r="Y46">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4369,7 +4369,7 @@
         <v>55</v>
       </c>
       <c r="B47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C47">
         <v>-1</v>
@@ -4378,13 +4378,13 @@
         <v>10</v>
       </c>
       <c r="E47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F47">
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H47">
         <v>-1</v>
@@ -4423,7 +4423,7 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U47">
         <v>-1</v>
@@ -4432,13 +4432,13 @@
         <v>10</v>
       </c>
       <c r="W47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X47">
         <v>-1</v>
       </c>
       <c r="Y47">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4561,27 +4561,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
       <c r="I4">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4590,27 +4593,30 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>7.9</v>
+      </c>
       <c r="I5">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4619,27 +4625,30 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>8.699999999999999</v>
+      </c>
       <c r="I6">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -4648,13 +4657,13 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -4663,10 +4672,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4676,7 +4685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4760,47 +4769,47 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920289</v>
+        <v>21330051920290</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920289</v>
+        <v>21330051920290</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4817,104 +4826,104 @@
         <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920290</v>
+        <v>21330051920291</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920290</v>
+        <v>21330051920291</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920290</v>
+        <v>21330051920292</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920290</v>
+        <v>21330051920292</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920291</v>
+        <v>21330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -4925,16 +4934,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920291</v>
+        <v>21330051920293</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4945,19 +4954,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920291</v>
+        <v>21330051920293</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
@@ -4965,56 +4974,56 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920291</v>
+        <v>21330051920294</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920291</v>
+        <v>21330051920294</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920292</v>
+        <v>21330051920295</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -5025,16 +5034,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920292</v>
+        <v>21330051920295</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -5045,76 +5054,76 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920292</v>
+        <v>21330051920296</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920292</v>
+        <v>21330051920296</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920292</v>
+        <v>21330051920296</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920293</v>
+        <v>21330051920297</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -5125,16 +5134,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920293</v>
+        <v>21330051920297</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -5145,376 +5154,376 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920293</v>
+        <v>21330051920297</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920293</v>
+        <v>21330051920298</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920293</v>
+        <v>21330051920298</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920294</v>
+        <v>21330051920298</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920294</v>
+        <v>21330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920294</v>
+        <v>21330051920299</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920294</v>
+        <v>21330051920299</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920294</v>
+        <v>21330051920299</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920295</v>
+        <v>21330051920299</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920295</v>
+        <v>21330051920337</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920295</v>
+        <v>21330051920337</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920295</v>
+        <v>21330051920337</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920295</v>
+        <v>21330051920300</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920296</v>
+        <v>21330051920300</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920296</v>
+        <v>21330051920301</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920296</v>
+        <v>21330051920301</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920296</v>
+        <v>21330051920302</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920296</v>
+        <v>21330051920302</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920297</v>
+        <v>21330051920303</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -5525,16 +5534,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920297</v>
+        <v>21330051920303</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E43" t="s">
         <v>6</v>
@@ -5545,19 +5554,19 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920297</v>
+        <v>21330051920303</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>67</v>
@@ -5565,239 +5574,239 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920297</v>
+        <v>21330051920304</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920297</v>
+        <v>21330051920304</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920298</v>
+        <v>21330051920305</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920298</v>
+        <v>21330051920305</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920298</v>
+        <v>21330051920305</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D49" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920298</v>
+        <v>21330051920306</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920298</v>
+        <v>21330051920306</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920298</v>
+        <v>21330051920306</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920299</v>
+        <v>20330051920235</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920299</v>
+        <v>20330051920235</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E54" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920299</v>
+        <v>20330051920235</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920299</v>
+        <v>20330051920235</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E56" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
         <v>67</v>
@@ -5805,56 +5814,56 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920299</v>
+        <v>21330051920307</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920299</v>
+        <v>21330051920307</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F58" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920337</v>
+        <v>21330051920308</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -5865,16 +5874,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920337</v>
+        <v>21330051920308</v>
       </c>
       <c r="B60" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E60" t="s">
         <v>6</v>
@@ -5885,19 +5894,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920337</v>
+        <v>21330051920308</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E61" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
         <v>67</v>
@@ -5905,56 +5914,56 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920337</v>
+        <v>21330051920309</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D62" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920337</v>
+        <v>21330051920309</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F63" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920300</v>
+        <v>21330051920090</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -5965,16 +5974,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920300</v>
+        <v>21330051920090</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E65" t="s">
         <v>6</v>
@@ -5985,176 +5994,176 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920300</v>
+        <v>21330051920310</v>
       </c>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E66" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920300</v>
+        <v>21330051920310</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D67" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920300</v>
+        <v>21330051920311</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920301</v>
+        <v>21330051920311</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E69" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920301</v>
+        <v>21330051920311</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920301</v>
+        <v>21330051920312</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E71" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920301</v>
+        <v>21330051920312</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D72" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F72" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920301</v>
+        <v>21330051920312</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920302</v>
+        <v>21330051920313</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -6165,16 +6174,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920302</v>
+        <v>21330051920313</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D75" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E75" t="s">
         <v>6</v>
@@ -6185,176 +6194,176 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920302</v>
+        <v>21330051920314</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920302</v>
+        <v>21330051920314</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F77" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>21330051920302</v>
+        <v>21330051920172</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D78" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>21330051920303</v>
+        <v>21330051920172</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C79" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="D79" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>21330051920303</v>
+        <v>21330051920315</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C80" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E80" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>21330051920303</v>
+        <v>21330051920315</v>
       </c>
       <c r="B81" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C81" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>21330051920303</v>
+        <v>21330051920316</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="D82" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F82" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>21330051920303</v>
+        <v>21330051920316</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="E83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F83" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>21330051920304</v>
+        <v>21330051920317</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D84" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -6365,16 +6374,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>21330051920304</v>
+        <v>21330051920317</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D85" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
         <v>6</v>
@@ -6385,276 +6394,276 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>21330051920304</v>
+        <v>21330051920318</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D86" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E86" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>21330051920304</v>
+        <v>21330051920318</v>
       </c>
       <c r="B87" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D87" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F87" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>21330051920304</v>
+        <v>21330051920319</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="E88" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>21330051920305</v>
+        <v>21330051920319</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C89" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E89" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>21330051920305</v>
+        <v>21330051920319</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E90" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91">
-        <v>21330051920305</v>
+        <v>21330051920320</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D91" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="E91" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>21330051920305</v>
+        <v>21330051920320</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D92" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F92" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>21330051920305</v>
+        <v>21330051920321</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E93" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>21330051920306</v>
+        <v>21330051920321</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E94" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>21330051920306</v>
+        <v>21330051920321</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E95" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>21330051920306</v>
+        <v>21330051920323</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E96" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>21330051920306</v>
+        <v>21330051920323</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D97" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F97" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>21330051920306</v>
+        <v>21330051920323</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C98" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D98" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E98" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>20330051920235</v>
+        <v>21330051920324</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D99" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -6665,16 +6674,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>20330051920235</v>
+        <v>21330051920324</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D100" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E100" t="s">
         <v>6</v>
@@ -6685,139 +6694,139 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>20330051920235</v>
+        <v>21330051920326</v>
       </c>
       <c r="B101" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C101" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E101" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F101" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>20330051920235</v>
+        <v>21330051920326</v>
       </c>
       <c r="B102" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C102" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D102" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F102" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>20330051920235</v>
+        <v>21330051920327</v>
       </c>
       <c r="B103" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C103" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="D103" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E103" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F103" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104">
-        <v>21330051920307</v>
+        <v>21330051920327</v>
       </c>
       <c r="B104" t="s">
+        <v>110</v>
+      </c>
+      <c r="C104" t="s">
         <v>92</v>
       </c>
-      <c r="C104" t="s">
-        <v>126</v>
-      </c>
       <c r="D104" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E104" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F104" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105">
-        <v>21330051920307</v>
+        <v>21330051920328</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D105" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E105" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106">
-        <v>21330051920307</v>
+        <v>21330051920328</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D106" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E106" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F106" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107">
-        <v>21330051920307</v>
+        <v>21330051920328</v>
       </c>
       <c r="B107" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F107" t="s">
         <v>68</v>
@@ -6825,36 +6834,36 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108">
-        <v>21330051920307</v>
+        <v>21330051920328</v>
       </c>
       <c r="B108" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C108" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="D108" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E108" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109">
-        <v>21330051920308</v>
+        <v>21330051920329</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D109" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -6865,16 +6874,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110">
-        <v>21330051920308</v>
+        <v>21330051920329</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D110" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
         <v>6</v>
@@ -6885,2262 +6894,42 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111">
-        <v>21330051920308</v>
+        <v>21330051920330</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C111" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D111" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E111" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F111" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112">
-        <v>21330051920308</v>
+        <v>21330051920330</v>
       </c>
       <c r="B112" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D112" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E112" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F112" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920308</v>
-      </c>
-      <c r="B113" t="s">
-        <v>93</v>
-      </c>
-      <c r="C113" t="s">
-        <v>127</v>
-      </c>
-      <c r="D113" t="s">
-        <v>163</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920309</v>
-      </c>
-      <c r="B114" t="s">
-        <v>94</v>
-      </c>
-      <c r="C114" t="s">
-        <v>99</v>
-      </c>
-      <c r="D114" t="s">
-        <v>164</v>
-      </c>
-      <c r="E114" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920309</v>
-      </c>
-      <c r="B115" t="s">
-        <v>94</v>
-      </c>
-      <c r="C115" t="s">
-        <v>99</v>
-      </c>
-      <c r="D115" t="s">
-        <v>164</v>
-      </c>
-      <c r="E115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920309</v>
-      </c>
-      <c r="B116" t="s">
-        <v>94</v>
-      </c>
-      <c r="C116" t="s">
-        <v>99</v>
-      </c>
-      <c r="D116" t="s">
-        <v>164</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920309</v>
-      </c>
-      <c r="B117" t="s">
-        <v>94</v>
-      </c>
-      <c r="C117" t="s">
-        <v>99</v>
-      </c>
-      <c r="D117" t="s">
-        <v>164</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920309</v>
-      </c>
-      <c r="B118" t="s">
-        <v>94</v>
-      </c>
-      <c r="C118" t="s">
-        <v>99</v>
-      </c>
-      <c r="D118" t="s">
-        <v>164</v>
-      </c>
-      <c r="E118" t="s">
-        <v>8</v>
-      </c>
-      <c r="F118" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920090</v>
-      </c>
-      <c r="B119" t="s">
-        <v>95</v>
-      </c>
-      <c r="C119" t="s">
-        <v>128</v>
-      </c>
-      <c r="D119" t="s">
-        <v>165</v>
-      </c>
-      <c r="E119" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>21330051920090</v>
-      </c>
-      <c r="B120" t="s">
-        <v>95</v>
-      </c>
-      <c r="C120" t="s">
-        <v>128</v>
-      </c>
-      <c r="D120" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>21330051920090</v>
-      </c>
-      <c r="B121" t="s">
-        <v>95</v>
-      </c>
-      <c r="C121" t="s">
-        <v>128</v>
-      </c>
-      <c r="D121" t="s">
-        <v>165</v>
-      </c>
-      <c r="E121" t="s">
-        <v>5</v>
-      </c>
-      <c r="F121" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>21330051920090</v>
-      </c>
-      <c r="B122" t="s">
-        <v>95</v>
-      </c>
-      <c r="C122" t="s">
-        <v>128</v>
-      </c>
-      <c r="D122" t="s">
-        <v>165</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>21330051920090</v>
-      </c>
-      <c r="B123" t="s">
-        <v>95</v>
-      </c>
-      <c r="C123" t="s">
-        <v>128</v>
-      </c>
-      <c r="D123" t="s">
-        <v>165</v>
-      </c>
-      <c r="E123" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>21330051920310</v>
-      </c>
-      <c r="B124" t="s">
-        <v>96</v>
-      </c>
-      <c r="C124" t="s">
-        <v>129</v>
-      </c>
-      <c r="D124" t="s">
-        <v>166</v>
-      </c>
-      <c r="E124" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>21330051920310</v>
-      </c>
-      <c r="B125" t="s">
-        <v>96</v>
-      </c>
-      <c r="C125" t="s">
-        <v>129</v>
-      </c>
-      <c r="D125" t="s">
-        <v>166</v>
-      </c>
-      <c r="E125" t="s">
-        <v>6</v>
-      </c>
-      <c r="F125" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>21330051920310</v>
-      </c>
-      <c r="B126" t="s">
-        <v>96</v>
-      </c>
-      <c r="C126" t="s">
-        <v>129</v>
-      </c>
-      <c r="D126" t="s">
-        <v>166</v>
-      </c>
-      <c r="E126" t="s">
-        <v>5</v>
-      </c>
-      <c r="F126" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>21330051920310</v>
-      </c>
-      <c r="B127" t="s">
-        <v>96</v>
-      </c>
-      <c r="C127" t="s">
-        <v>129</v>
-      </c>
-      <c r="D127" t="s">
-        <v>166</v>
-      </c>
-      <c r="E127" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>21330051920310</v>
-      </c>
-      <c r="B128" t="s">
-        <v>96</v>
-      </c>
-      <c r="C128" t="s">
-        <v>129</v>
-      </c>
-      <c r="D128" t="s">
-        <v>166</v>
-      </c>
-      <c r="E128" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>21330051920311</v>
-      </c>
-      <c r="B129" t="s">
-        <v>97</v>
-      </c>
-      <c r="C129" t="s">
-        <v>130</v>
-      </c>
-      <c r="D129" t="s">
-        <v>167</v>
-      </c>
-      <c r="E129" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>21330051920311</v>
-      </c>
-      <c r="B130" t="s">
-        <v>97</v>
-      </c>
-      <c r="C130" t="s">
-        <v>130</v>
-      </c>
-      <c r="D130" t="s">
-        <v>167</v>
-      </c>
-      <c r="E130" t="s">
-        <v>6</v>
-      </c>
-      <c r="F130" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>21330051920311</v>
-      </c>
-      <c r="B131" t="s">
-        <v>97</v>
-      </c>
-      <c r="C131" t="s">
-        <v>130</v>
-      </c>
-      <c r="D131" t="s">
-        <v>167</v>
-      </c>
-      <c r="E131" t="s">
-        <v>5</v>
-      </c>
-      <c r="F131" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>21330051920311</v>
-      </c>
-      <c r="B132" t="s">
-        <v>97</v>
-      </c>
-      <c r="C132" t="s">
-        <v>130</v>
-      </c>
-      <c r="D132" t="s">
-        <v>167</v>
-      </c>
-      <c r="E132" t="s">
-        <v>10</v>
-      </c>
-      <c r="F132" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>21330051920311</v>
-      </c>
-      <c r="B133" t="s">
-        <v>97</v>
-      </c>
-      <c r="C133" t="s">
-        <v>130</v>
-      </c>
-      <c r="D133" t="s">
-        <v>167</v>
-      </c>
-      <c r="E133" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>21330051920312</v>
-      </c>
-      <c r="B134" t="s">
-        <v>98</v>
-      </c>
-      <c r="C134" t="s">
-        <v>125</v>
-      </c>
-      <c r="D134" t="s">
-        <v>168</v>
-      </c>
-      <c r="E134" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>21330051920312</v>
-      </c>
-      <c r="B135" t="s">
-        <v>98</v>
-      </c>
-      <c r="C135" t="s">
-        <v>125</v>
-      </c>
-      <c r="D135" t="s">
-        <v>168</v>
-      </c>
-      <c r="E135" t="s">
-        <v>6</v>
-      </c>
-      <c r="F135" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>21330051920312</v>
-      </c>
-      <c r="B136" t="s">
-        <v>98</v>
-      </c>
-      <c r="C136" t="s">
-        <v>125</v>
-      </c>
-      <c r="D136" t="s">
-        <v>168</v>
-      </c>
-      <c r="E136" t="s">
-        <v>5</v>
-      </c>
-      <c r="F136" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>21330051920312</v>
-      </c>
-      <c r="B137" t="s">
-        <v>98</v>
-      </c>
-      <c r="C137" t="s">
-        <v>125</v>
-      </c>
-      <c r="D137" t="s">
-        <v>168</v>
-      </c>
-      <c r="E137" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>21330051920312</v>
-      </c>
-      <c r="B138" t="s">
-        <v>98</v>
-      </c>
-      <c r="C138" t="s">
-        <v>125</v>
-      </c>
-      <c r="D138" t="s">
-        <v>168</v>
-      </c>
-      <c r="E138" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>21330051920313</v>
-      </c>
-      <c r="B139" t="s">
-        <v>99</v>
-      </c>
-      <c r="C139" t="s">
-        <v>94</v>
-      </c>
-      <c r="D139" t="s">
-        <v>169</v>
-      </c>
-      <c r="E139" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>21330051920313</v>
-      </c>
-      <c r="B140" t="s">
-        <v>99</v>
-      </c>
-      <c r="C140" t="s">
-        <v>94</v>
-      </c>
-      <c r="D140" t="s">
-        <v>169</v>
-      </c>
-      <c r="E140" t="s">
-        <v>6</v>
-      </c>
-      <c r="F140" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>21330051920313</v>
-      </c>
-      <c r="B141" t="s">
-        <v>99</v>
-      </c>
-      <c r="C141" t="s">
-        <v>94</v>
-      </c>
-      <c r="D141" t="s">
-        <v>169</v>
-      </c>
-      <c r="E141" t="s">
-        <v>5</v>
-      </c>
-      <c r="F141" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>21330051920313</v>
-      </c>
-      <c r="B142" t="s">
-        <v>99</v>
-      </c>
-      <c r="C142" t="s">
-        <v>94</v>
-      </c>
-      <c r="D142" t="s">
-        <v>169</v>
-      </c>
-      <c r="E142" t="s">
-        <v>10</v>
-      </c>
-      <c r="F142" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>21330051920313</v>
-      </c>
-      <c r="B143" t="s">
-        <v>99</v>
-      </c>
-      <c r="C143" t="s">
-        <v>94</v>
-      </c>
-      <c r="D143" t="s">
-        <v>169</v>
-      </c>
-      <c r="E143" t="s">
-        <v>8</v>
-      </c>
-      <c r="F143" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>21330051920314</v>
-      </c>
-      <c r="B144" t="s">
-        <v>100</v>
-      </c>
-      <c r="C144" t="s">
-        <v>93</v>
-      </c>
-      <c r="D144" t="s">
-        <v>170</v>
-      </c>
-      <c r="E144" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>21330051920314</v>
-      </c>
-      <c r="B145" t="s">
-        <v>100</v>
-      </c>
-      <c r="C145" t="s">
-        <v>93</v>
-      </c>
-      <c r="D145" t="s">
-        <v>170</v>
-      </c>
-      <c r="E145" t="s">
-        <v>6</v>
-      </c>
-      <c r="F145" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>21330051920314</v>
-      </c>
-      <c r="B146" t="s">
-        <v>100</v>
-      </c>
-      <c r="C146" t="s">
-        <v>93</v>
-      </c>
-      <c r="D146" t="s">
-        <v>170</v>
-      </c>
-      <c r="E146" t="s">
-        <v>5</v>
-      </c>
-      <c r="F146" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>21330051920314</v>
-      </c>
-      <c r="B147" t="s">
-        <v>100</v>
-      </c>
-      <c r="C147" t="s">
-        <v>93</v>
-      </c>
-      <c r="D147" t="s">
-        <v>170</v>
-      </c>
-      <c r="E147" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>21330051920314</v>
-      </c>
-      <c r="B148" t="s">
-        <v>100</v>
-      </c>
-      <c r="C148" t="s">
-        <v>93</v>
-      </c>
-      <c r="D148" t="s">
-        <v>170</v>
-      </c>
-      <c r="E148" t="s">
-        <v>8</v>
-      </c>
-      <c r="F148" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>21330051920172</v>
-      </c>
-      <c r="B149" t="s">
-        <v>101</v>
-      </c>
-      <c r="C149" t="s">
-        <v>131</v>
-      </c>
-      <c r="D149" t="s">
-        <v>171</v>
-      </c>
-      <c r="E149" t="s">
-        <v>9</v>
-      </c>
-      <c r="F149" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>21330051920172</v>
-      </c>
-      <c r="B150" t="s">
-        <v>101</v>
-      </c>
-      <c r="C150" t="s">
-        <v>131</v>
-      </c>
-      <c r="D150" t="s">
-        <v>171</v>
-      </c>
-      <c r="E150" t="s">
-        <v>6</v>
-      </c>
-      <c r="F150" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>21330051920172</v>
-      </c>
-      <c r="B151" t="s">
-        <v>101</v>
-      </c>
-      <c r="C151" t="s">
-        <v>131</v>
-      </c>
-      <c r="D151" t="s">
-        <v>171</v>
-      </c>
-      <c r="E151" t="s">
-        <v>5</v>
-      </c>
-      <c r="F151" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>21330051920172</v>
-      </c>
-      <c r="B152" t="s">
-        <v>101</v>
-      </c>
-      <c r="C152" t="s">
-        <v>131</v>
-      </c>
-      <c r="D152" t="s">
-        <v>171</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>21330051920172</v>
-      </c>
-      <c r="B153" t="s">
-        <v>101</v>
-      </c>
-      <c r="C153" t="s">
-        <v>131</v>
-      </c>
-      <c r="D153" t="s">
-        <v>171</v>
-      </c>
-      <c r="E153" t="s">
-        <v>8</v>
-      </c>
-      <c r="F153" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>21330051920315</v>
-      </c>
-      <c r="B154" t="s">
-        <v>102</v>
-      </c>
-      <c r="C154" t="s">
-        <v>132</v>
-      </c>
-      <c r="D154" t="s">
-        <v>172</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>21330051920315</v>
-      </c>
-      <c r="B155" t="s">
-        <v>102</v>
-      </c>
-      <c r="C155" t="s">
-        <v>132</v>
-      </c>
-      <c r="D155" t="s">
-        <v>172</v>
-      </c>
-      <c r="E155" t="s">
-        <v>6</v>
-      </c>
-      <c r="F155" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>21330051920315</v>
-      </c>
-      <c r="B156" t="s">
-        <v>102</v>
-      </c>
-      <c r="C156" t="s">
-        <v>132</v>
-      </c>
-      <c r="D156" t="s">
-        <v>172</v>
-      </c>
-      <c r="E156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>21330051920315</v>
-      </c>
-      <c r="B157" t="s">
-        <v>102</v>
-      </c>
-      <c r="C157" t="s">
-        <v>132</v>
-      </c>
-      <c r="D157" t="s">
-        <v>172</v>
-      </c>
-      <c r="E157" t="s">
-        <v>10</v>
-      </c>
-      <c r="F157" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>21330051920315</v>
-      </c>
-      <c r="B158" t="s">
-        <v>102</v>
-      </c>
-      <c r="C158" t="s">
-        <v>132</v>
-      </c>
-      <c r="D158" t="s">
-        <v>172</v>
-      </c>
-      <c r="E158" t="s">
-        <v>8</v>
-      </c>
-      <c r="F158" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>21330051920316</v>
-      </c>
-      <c r="B159" t="s">
-        <v>103</v>
-      </c>
-      <c r="C159" t="s">
-        <v>133</v>
-      </c>
-      <c r="D159" t="s">
-        <v>169</v>
-      </c>
-      <c r="E159" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>21330051920316</v>
-      </c>
-      <c r="B160" t="s">
-        <v>103</v>
-      </c>
-      <c r="C160" t="s">
-        <v>133</v>
-      </c>
-      <c r="D160" t="s">
-        <v>169</v>
-      </c>
-      <c r="E160" t="s">
-        <v>6</v>
-      </c>
-      <c r="F160" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>21330051920316</v>
-      </c>
-      <c r="B161" t="s">
-        <v>103</v>
-      </c>
-      <c r="C161" t="s">
-        <v>133</v>
-      </c>
-      <c r="D161" t="s">
-        <v>169</v>
-      </c>
-      <c r="E161" t="s">
-        <v>5</v>
-      </c>
-      <c r="F161" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>21330051920316</v>
-      </c>
-      <c r="B162" t="s">
-        <v>103</v>
-      </c>
-      <c r="C162" t="s">
-        <v>133</v>
-      </c>
-      <c r="D162" t="s">
-        <v>169</v>
-      </c>
-      <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>21330051920316</v>
-      </c>
-      <c r="B163" t="s">
-        <v>103</v>
-      </c>
-      <c r="C163" t="s">
-        <v>133</v>
-      </c>
-      <c r="D163" t="s">
-        <v>169</v>
-      </c>
-      <c r="E163" t="s">
-        <v>8</v>
-      </c>
-      <c r="F163" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>21330051920317</v>
-      </c>
-      <c r="B164" t="s">
-        <v>104</v>
-      </c>
-      <c r="C164" t="s">
-        <v>134</v>
-      </c>
-      <c r="D164" t="s">
-        <v>173</v>
-      </c>
-      <c r="E164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>21330051920317</v>
-      </c>
-      <c r="B165" t="s">
-        <v>104</v>
-      </c>
-      <c r="C165" t="s">
-        <v>134</v>
-      </c>
-      <c r="D165" t="s">
-        <v>173</v>
-      </c>
-      <c r="E165" t="s">
-        <v>6</v>
-      </c>
-      <c r="F165" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>21330051920317</v>
-      </c>
-      <c r="B166" t="s">
-        <v>104</v>
-      </c>
-      <c r="C166" t="s">
-        <v>134</v>
-      </c>
-      <c r="D166" t="s">
-        <v>173</v>
-      </c>
-      <c r="E166" t="s">
-        <v>5</v>
-      </c>
-      <c r="F166" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>21330051920317</v>
-      </c>
-      <c r="B167" t="s">
-        <v>104</v>
-      </c>
-      <c r="C167" t="s">
-        <v>134</v>
-      </c>
-      <c r="D167" t="s">
-        <v>173</v>
-      </c>
-      <c r="E167" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>21330051920317</v>
-      </c>
-      <c r="B168" t="s">
-        <v>104</v>
-      </c>
-      <c r="C168" t="s">
-        <v>134</v>
-      </c>
-      <c r="D168" t="s">
-        <v>173</v>
-      </c>
-      <c r="E168" t="s">
-        <v>8</v>
-      </c>
-      <c r="F168" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>21330051920318</v>
-      </c>
-      <c r="B169" t="s">
-        <v>105</v>
-      </c>
-      <c r="C169" t="s">
-        <v>135</v>
-      </c>
-      <c r="D169" t="s">
-        <v>174</v>
-      </c>
-      <c r="E169" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>21330051920318</v>
-      </c>
-      <c r="B170" t="s">
-        <v>105</v>
-      </c>
-      <c r="C170" t="s">
-        <v>135</v>
-      </c>
-      <c r="D170" t="s">
-        <v>174</v>
-      </c>
-      <c r="E170" t="s">
-        <v>6</v>
-      </c>
-      <c r="F170" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>21330051920318</v>
-      </c>
-      <c r="B171" t="s">
-        <v>105</v>
-      </c>
-      <c r="C171" t="s">
-        <v>135</v>
-      </c>
-      <c r="D171" t="s">
-        <v>174</v>
-      </c>
-      <c r="E171" t="s">
-        <v>5</v>
-      </c>
-      <c r="F171" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>21330051920318</v>
-      </c>
-      <c r="B172" t="s">
-        <v>105</v>
-      </c>
-      <c r="C172" t="s">
-        <v>135</v>
-      </c>
-      <c r="D172" t="s">
-        <v>174</v>
-      </c>
-      <c r="E172" t="s">
-        <v>10</v>
-      </c>
-      <c r="F172" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>21330051920318</v>
-      </c>
-      <c r="B173" t="s">
-        <v>105</v>
-      </c>
-      <c r="C173" t="s">
-        <v>135</v>
-      </c>
-      <c r="D173" t="s">
-        <v>174</v>
-      </c>
-      <c r="E173" t="s">
-        <v>8</v>
-      </c>
-      <c r="F173" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174">
-        <v>21330051920319</v>
-      </c>
-      <c r="B174" t="s">
-        <v>105</v>
-      </c>
-      <c r="C174" t="s">
-        <v>114</v>
-      </c>
-      <c r="D174" t="s">
-        <v>175</v>
-      </c>
-      <c r="E174" t="s">
-        <v>9</v>
-      </c>
-      <c r="F174" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175">
-        <v>21330051920319</v>
-      </c>
-      <c r="B175" t="s">
-        <v>105</v>
-      </c>
-      <c r="C175" t="s">
-        <v>114</v>
-      </c>
-      <c r="D175" t="s">
-        <v>175</v>
-      </c>
-      <c r="E175" t="s">
-        <v>6</v>
-      </c>
-      <c r="F175" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176">
-        <v>21330051920319</v>
-      </c>
-      <c r="B176" t="s">
-        <v>105</v>
-      </c>
-      <c r="C176" t="s">
-        <v>114</v>
-      </c>
-      <c r="D176" t="s">
-        <v>175</v>
-      </c>
-      <c r="E176" t="s">
-        <v>5</v>
-      </c>
-      <c r="F176" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177">
-        <v>21330051920319</v>
-      </c>
-      <c r="B177" t="s">
-        <v>105</v>
-      </c>
-      <c r="C177" t="s">
-        <v>114</v>
-      </c>
-      <c r="D177" t="s">
-        <v>175</v>
-      </c>
-      <c r="E177" t="s">
-        <v>10</v>
-      </c>
-      <c r="F177" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178">
-        <v>21330051920319</v>
-      </c>
-      <c r="B178" t="s">
-        <v>105</v>
-      </c>
-      <c r="C178" t="s">
-        <v>114</v>
-      </c>
-      <c r="D178" t="s">
-        <v>175</v>
-      </c>
-      <c r="E178" t="s">
-        <v>8</v>
-      </c>
-      <c r="F178" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179">
-        <v>21330051920320</v>
-      </c>
-      <c r="B179" t="s">
-        <v>106</v>
-      </c>
-      <c r="C179" t="s">
-        <v>136</v>
-      </c>
-      <c r="D179" t="s">
-        <v>176</v>
-      </c>
-      <c r="E179" t="s">
-        <v>9</v>
-      </c>
-      <c r="F179" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180">
-        <v>21330051920320</v>
-      </c>
-      <c r="B180" t="s">
-        <v>106</v>
-      </c>
-      <c r="C180" t="s">
-        <v>136</v>
-      </c>
-      <c r="D180" t="s">
-        <v>176</v>
-      </c>
-      <c r="E180" t="s">
-        <v>6</v>
-      </c>
-      <c r="F180" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181">
-        <v>21330051920320</v>
-      </c>
-      <c r="B181" t="s">
-        <v>106</v>
-      </c>
-      <c r="C181" t="s">
-        <v>136</v>
-      </c>
-      <c r="D181" t="s">
-        <v>176</v>
-      </c>
-      <c r="E181" t="s">
-        <v>5</v>
-      </c>
-      <c r="F181" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182">
-        <v>21330051920320</v>
-      </c>
-      <c r="B182" t="s">
-        <v>106</v>
-      </c>
-      <c r="C182" t="s">
-        <v>136</v>
-      </c>
-      <c r="D182" t="s">
-        <v>176</v>
-      </c>
-      <c r="E182" t="s">
-        <v>10</v>
-      </c>
-      <c r="F182" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183">
-        <v>21330051920320</v>
-      </c>
-      <c r="B183" t="s">
-        <v>106</v>
-      </c>
-      <c r="C183" t="s">
-        <v>136</v>
-      </c>
-      <c r="D183" t="s">
-        <v>176</v>
-      </c>
-      <c r="E183" t="s">
-        <v>8</v>
-      </c>
-      <c r="F183" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184">
-        <v>21330051920321</v>
-      </c>
-      <c r="B184" t="s">
-        <v>106</v>
-      </c>
-      <c r="C184" t="s">
-        <v>137</v>
-      </c>
-      <c r="D184" t="s">
-        <v>177</v>
-      </c>
-      <c r="E184" t="s">
-        <v>9</v>
-      </c>
-      <c r="F184" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185">
-        <v>21330051920321</v>
-      </c>
-      <c r="B185" t="s">
-        <v>106</v>
-      </c>
-      <c r="C185" t="s">
-        <v>137</v>
-      </c>
-      <c r="D185" t="s">
-        <v>177</v>
-      </c>
-      <c r="E185" t="s">
-        <v>6</v>
-      </c>
-      <c r="F185" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186">
-        <v>21330051920321</v>
-      </c>
-      <c r="B186" t="s">
-        <v>106</v>
-      </c>
-      <c r="C186" t="s">
-        <v>137</v>
-      </c>
-      <c r="D186" t="s">
-        <v>177</v>
-      </c>
-      <c r="E186" t="s">
-        <v>5</v>
-      </c>
-      <c r="F186" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187">
-        <v>21330051920321</v>
-      </c>
-      <c r="B187" t="s">
-        <v>106</v>
-      </c>
-      <c r="C187" t="s">
-        <v>137</v>
-      </c>
-      <c r="D187" t="s">
-        <v>177</v>
-      </c>
-      <c r="E187" t="s">
-        <v>10</v>
-      </c>
-      <c r="F187" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188">
-        <v>21330051920321</v>
-      </c>
-      <c r="B188" t="s">
-        <v>106</v>
-      </c>
-      <c r="C188" t="s">
-        <v>137</v>
-      </c>
-      <c r="D188" t="s">
-        <v>177</v>
-      </c>
-      <c r="E188" t="s">
-        <v>8</v>
-      </c>
-      <c r="F188" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189">
-        <v>21330051920323</v>
-      </c>
-      <c r="B189" t="s">
-        <v>107</v>
-      </c>
-      <c r="C189" t="s">
-        <v>125</v>
-      </c>
-      <c r="D189" t="s">
-        <v>178</v>
-      </c>
-      <c r="E189" t="s">
-        <v>9</v>
-      </c>
-      <c r="F189" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190">
-        <v>21330051920323</v>
-      </c>
-      <c r="B190" t="s">
-        <v>107</v>
-      </c>
-      <c r="C190" t="s">
-        <v>125</v>
-      </c>
-      <c r="D190" t="s">
-        <v>178</v>
-      </c>
-      <c r="E190" t="s">
-        <v>6</v>
-      </c>
-      <c r="F190" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191">
-        <v>21330051920323</v>
-      </c>
-      <c r="B191" t="s">
-        <v>107</v>
-      </c>
-      <c r="C191" t="s">
-        <v>125</v>
-      </c>
-      <c r="D191" t="s">
-        <v>178</v>
-      </c>
-      <c r="E191" t="s">
-        <v>5</v>
-      </c>
-      <c r="F191" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192">
-        <v>21330051920323</v>
-      </c>
-      <c r="B192" t="s">
-        <v>107</v>
-      </c>
-      <c r="C192" t="s">
-        <v>125</v>
-      </c>
-      <c r="D192" t="s">
-        <v>178</v>
-      </c>
-      <c r="E192" t="s">
-        <v>10</v>
-      </c>
-      <c r="F192" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193">
-        <v>21330051920323</v>
-      </c>
-      <c r="B193" t="s">
-        <v>107</v>
-      </c>
-      <c r="C193" t="s">
-        <v>125</v>
-      </c>
-      <c r="D193" t="s">
-        <v>178</v>
-      </c>
-      <c r="E193" t="s">
-        <v>8</v>
-      </c>
-      <c r="F193" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194">
-        <v>21330051920324</v>
-      </c>
-      <c r="B194" t="s">
-        <v>108</v>
-      </c>
-      <c r="C194" t="s">
-        <v>138</v>
-      </c>
-      <c r="D194" t="s">
-        <v>179</v>
-      </c>
-      <c r="E194" t="s">
-        <v>9</v>
-      </c>
-      <c r="F194" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6">
-      <c r="A195">
-        <v>21330051920324</v>
-      </c>
-      <c r="B195" t="s">
-        <v>108</v>
-      </c>
-      <c r="C195" t="s">
-        <v>138</v>
-      </c>
-      <c r="D195" t="s">
-        <v>179</v>
-      </c>
-      <c r="E195" t="s">
-        <v>6</v>
-      </c>
-      <c r="F195" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196">
-        <v>21330051920324</v>
-      </c>
-      <c r="B196" t="s">
-        <v>108</v>
-      </c>
-      <c r="C196" t="s">
-        <v>138</v>
-      </c>
-      <c r="D196" t="s">
-        <v>179</v>
-      </c>
-      <c r="E196" t="s">
-        <v>5</v>
-      </c>
-      <c r="F196" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197">
-        <v>21330051920324</v>
-      </c>
-      <c r="B197" t="s">
-        <v>108</v>
-      </c>
-      <c r="C197" t="s">
-        <v>138</v>
-      </c>
-      <c r="D197" t="s">
-        <v>179</v>
-      </c>
-      <c r="E197" t="s">
-        <v>10</v>
-      </c>
-      <c r="F197" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198">
-        <v>21330051920324</v>
-      </c>
-      <c r="B198" t="s">
-        <v>108</v>
-      </c>
-      <c r="C198" t="s">
-        <v>138</v>
-      </c>
-      <c r="D198" t="s">
-        <v>179</v>
-      </c>
-      <c r="E198" t="s">
-        <v>8</v>
-      </c>
-      <c r="F198" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6">
-      <c r="A199">
-        <v>21330051920326</v>
-      </c>
-      <c r="B199" t="s">
-        <v>109</v>
-      </c>
-      <c r="C199" t="s">
-        <v>105</v>
-      </c>
-      <c r="D199" t="s">
-        <v>180</v>
-      </c>
-      <c r="E199" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6">
-      <c r="A200">
-        <v>21330051920326</v>
-      </c>
-      <c r="B200" t="s">
-        <v>109</v>
-      </c>
-      <c r="C200" t="s">
-        <v>105</v>
-      </c>
-      <c r="D200" t="s">
-        <v>180</v>
-      </c>
-      <c r="E200" t="s">
-        <v>6</v>
-      </c>
-      <c r="F200" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6">
-      <c r="A201">
-        <v>21330051920326</v>
-      </c>
-      <c r="B201" t="s">
-        <v>109</v>
-      </c>
-      <c r="C201" t="s">
-        <v>105</v>
-      </c>
-      <c r="D201" t="s">
-        <v>180</v>
-      </c>
-      <c r="E201" t="s">
-        <v>5</v>
-      </c>
-      <c r="F201" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6">
-      <c r="A202">
-        <v>21330051920326</v>
-      </c>
-      <c r="B202" t="s">
-        <v>109</v>
-      </c>
-      <c r="C202" t="s">
-        <v>105</v>
-      </c>
-      <c r="D202" t="s">
-        <v>180</v>
-      </c>
-      <c r="E202" t="s">
-        <v>10</v>
-      </c>
-      <c r="F202" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6">
-      <c r="A203">
-        <v>21330051920326</v>
-      </c>
-      <c r="B203" t="s">
-        <v>109</v>
-      </c>
-      <c r="C203" t="s">
-        <v>105</v>
-      </c>
-      <c r="D203" t="s">
-        <v>180</v>
-      </c>
-      <c r="E203" t="s">
-        <v>8</v>
-      </c>
-      <c r="F203" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6">
-      <c r="A204">
-        <v>21330051920327</v>
-      </c>
-      <c r="B204" t="s">
-        <v>110</v>
-      </c>
-      <c r="C204" t="s">
-        <v>92</v>
-      </c>
-      <c r="D204" t="s">
-        <v>181</v>
-      </c>
-      <c r="E204" t="s">
-        <v>9</v>
-      </c>
-      <c r="F204" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6">
-      <c r="A205">
-        <v>21330051920327</v>
-      </c>
-      <c r="B205" t="s">
-        <v>110</v>
-      </c>
-      <c r="C205" t="s">
-        <v>92</v>
-      </c>
-      <c r="D205" t="s">
-        <v>181</v>
-      </c>
-      <c r="E205" t="s">
-        <v>6</v>
-      </c>
-      <c r="F205" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6">
-      <c r="A206">
-        <v>21330051920327</v>
-      </c>
-      <c r="B206" t="s">
-        <v>110</v>
-      </c>
-      <c r="C206" t="s">
-        <v>92</v>
-      </c>
-      <c r="D206" t="s">
-        <v>181</v>
-      </c>
-      <c r="E206" t="s">
-        <v>5</v>
-      </c>
-      <c r="F206" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6">
-      <c r="A207">
-        <v>21330051920327</v>
-      </c>
-      <c r="B207" t="s">
-        <v>110</v>
-      </c>
-      <c r="C207" t="s">
-        <v>92</v>
-      </c>
-      <c r="D207" t="s">
-        <v>181</v>
-      </c>
-      <c r="E207" t="s">
-        <v>10</v>
-      </c>
-      <c r="F207" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6">
-      <c r="A208">
-        <v>21330051920327</v>
-      </c>
-      <c r="B208" t="s">
-        <v>110</v>
-      </c>
-      <c r="C208" t="s">
-        <v>92</v>
-      </c>
-      <c r="D208" t="s">
-        <v>181</v>
-      </c>
-      <c r="E208" t="s">
-        <v>8</v>
-      </c>
-      <c r="F208" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6">
-      <c r="A209">
-        <v>21330051920328</v>
-      </c>
-      <c r="B209" t="s">
-        <v>111</v>
-      </c>
-      <c r="C209" t="s">
-        <v>139</v>
-      </c>
-      <c r="D209" t="s">
-        <v>182</v>
-      </c>
-      <c r="E209" t="s">
-        <v>9</v>
-      </c>
-      <c r="F209" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6">
-      <c r="A210">
-        <v>21330051920328</v>
-      </c>
-      <c r="B210" t="s">
-        <v>111</v>
-      </c>
-      <c r="C210" t="s">
-        <v>139</v>
-      </c>
-      <c r="D210" t="s">
-        <v>182</v>
-      </c>
-      <c r="E210" t="s">
-        <v>6</v>
-      </c>
-      <c r="F210" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6">
-      <c r="A211">
-        <v>21330051920328</v>
-      </c>
-      <c r="B211" t="s">
-        <v>111</v>
-      </c>
-      <c r="C211" t="s">
-        <v>139</v>
-      </c>
-      <c r="D211" t="s">
-        <v>182</v>
-      </c>
-      <c r="E211" t="s">
-        <v>5</v>
-      </c>
-      <c r="F211" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6">
-      <c r="A212">
-        <v>21330051920328</v>
-      </c>
-      <c r="B212" t="s">
-        <v>111</v>
-      </c>
-      <c r="C212" t="s">
-        <v>139</v>
-      </c>
-      <c r="D212" t="s">
-        <v>182</v>
-      </c>
-      <c r="E212" t="s">
-        <v>10</v>
-      </c>
-      <c r="F212" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6">
-      <c r="A213">
-        <v>21330051920328</v>
-      </c>
-      <c r="B213" t="s">
-        <v>111</v>
-      </c>
-      <c r="C213" t="s">
-        <v>139</v>
-      </c>
-      <c r="D213" t="s">
-        <v>182</v>
-      </c>
-      <c r="E213" t="s">
-        <v>8</v>
-      </c>
-      <c r="F213" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6">
-      <c r="A214">
-        <v>21330051920329</v>
-      </c>
-      <c r="B214" t="s">
-        <v>112</v>
-      </c>
-      <c r="C214" t="s">
-        <v>140</v>
-      </c>
-      <c r="D214" t="s">
-        <v>183</v>
-      </c>
-      <c r="E214" t="s">
-        <v>9</v>
-      </c>
-      <c r="F214" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6">
-      <c r="A215">
-        <v>21330051920329</v>
-      </c>
-      <c r="B215" t="s">
-        <v>112</v>
-      </c>
-      <c r="C215" t="s">
-        <v>140</v>
-      </c>
-      <c r="D215" t="s">
-        <v>183</v>
-      </c>
-      <c r="E215" t="s">
-        <v>6</v>
-      </c>
-      <c r="F215" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6">
-      <c r="A216">
-        <v>21330051920329</v>
-      </c>
-      <c r="B216" t="s">
-        <v>112</v>
-      </c>
-      <c r="C216" t="s">
-        <v>140</v>
-      </c>
-      <c r="D216" t="s">
-        <v>183</v>
-      </c>
-      <c r="E216" t="s">
-        <v>5</v>
-      </c>
-      <c r="F216" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6">
-      <c r="A217">
-        <v>21330051920329</v>
-      </c>
-      <c r="B217" t="s">
-        <v>112</v>
-      </c>
-      <c r="C217" t="s">
-        <v>140</v>
-      </c>
-      <c r="D217" t="s">
-        <v>183</v>
-      </c>
-      <c r="E217" t="s">
-        <v>10</v>
-      </c>
-      <c r="F217" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6">
-      <c r="A218">
-        <v>21330051920329</v>
-      </c>
-      <c r="B218" t="s">
-        <v>112</v>
-      </c>
-      <c r="C218" t="s">
-        <v>140</v>
-      </c>
-      <c r="D218" t="s">
-        <v>183</v>
-      </c>
-      <c r="E218" t="s">
-        <v>8</v>
-      </c>
-      <c r="F218" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6">
-      <c r="A219">
-        <v>21330051920330</v>
-      </c>
-      <c r="B219" t="s">
-        <v>113</v>
-      </c>
-      <c r="C219" t="s">
-        <v>141</v>
-      </c>
-      <c r="D219" t="s">
-        <v>184</v>
-      </c>
-      <c r="E219" t="s">
-        <v>9</v>
-      </c>
-      <c r="F219" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6">
-      <c r="A220">
-        <v>21330051920330</v>
-      </c>
-      <c r="B220" t="s">
-        <v>113</v>
-      </c>
-      <c r="C220" t="s">
-        <v>141</v>
-      </c>
-      <c r="D220" t="s">
-        <v>184</v>
-      </c>
-      <c r="E220" t="s">
-        <v>6</v>
-      </c>
-      <c r="F220" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6">
-      <c r="A221">
-        <v>21330051920330</v>
-      </c>
-      <c r="B221" t="s">
-        <v>113</v>
-      </c>
-      <c r="C221" t="s">
-        <v>141</v>
-      </c>
-      <c r="D221" t="s">
-        <v>184</v>
-      </c>
-      <c r="E221" t="s">
-        <v>5</v>
-      </c>
-      <c r="F221" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6">
-      <c r="A222">
-        <v>21330051920330</v>
-      </c>
-      <c r="B222" t="s">
-        <v>113</v>
-      </c>
-      <c r="C222" t="s">
-        <v>141</v>
-      </c>
-      <c r="D222" t="s">
-        <v>184</v>
-      </c>
-      <c r="E222" t="s">
-        <v>10</v>
-      </c>
-      <c r="F222" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6">
-      <c r="A223">
-        <v>21330051920330</v>
-      </c>
-      <c r="B223" t="s">
-        <v>113</v>
-      </c>
-      <c r="C223" t="s">
-        <v>141</v>
-      </c>
-      <c r="D223" t="s">
-        <v>184</v>
-      </c>
-      <c r="E223" t="s">
-        <v>8</v>
-      </c>
-      <c r="F223" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -9188,7 +6977,7 @@
         <v>151</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9205,75 +6994,75 @@
         <v>152</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920289</v>
+        <v>20330051920235</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920290</v>
+        <v>21330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920291</v>
+        <v>21330051920289</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920292</v>
+        <v>21330051920290</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9290,602 +7079,602 @@
         <v>146</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920294</v>
+        <v>21330051920296</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920295</v>
+        <v>21330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920296</v>
+        <v>21330051920337</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920297</v>
+        <v>21330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920337</v>
+        <v>21330051920305</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920300</v>
+        <v>21330051920306</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920301</v>
+        <v>21330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920302</v>
+        <v>21330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920303</v>
+        <v>21330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920304</v>
+        <v>21330051920319</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920305</v>
+        <v>21330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920306</v>
+        <v>21330051920323</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920235</v>
+        <v>21330051920291</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920307</v>
+        <v>21330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920308</v>
+        <v>21330051920294</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920309</v>
+        <v>21330051920295</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920090</v>
+        <v>21330051920300</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920310</v>
+        <v>21330051920301</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920311</v>
+        <v>21330051920302</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920312</v>
+        <v>21330051920304</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920313</v>
+        <v>21330051920307</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920314</v>
+        <v>21330051920309</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920172</v>
+        <v>21330051920090</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920315</v>
+        <v>21330051920310</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920316</v>
+        <v>21330051920313</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
         <v>169</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920317</v>
+        <v>21330051920314</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920318</v>
+        <v>21330051920172</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920319</v>
+        <v>21330051920315</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920320</v>
+        <v>21330051920316</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920321</v>
+        <v>21330051920317</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920323</v>
+        <v>21330051920318</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E39">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920324</v>
+        <v>21330051920320</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920326</v>
+        <v>21330051920324</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920327</v>
+        <v>21330051920326</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920328</v>
+        <v>21330051920327</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9902,7 +7691,7 @@
         <v>183</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9919,7 +7708,7 @@
         <v>184</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9929,7 +7718,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9959,6 +7748,1156 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920291</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920292</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920292</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920294</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920294</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920295</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920295</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920300</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920300</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920301</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920301</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920302</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920302</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920304</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920304</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920307</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920307</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920309</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920309</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920090</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920090</v>
+      </c>
+      <c r="B23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920310</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920310</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920313</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920313</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920314</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920314</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920315</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920315</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920316</v>
+      </c>
+      <c r="B34" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920316</v>
+      </c>
+      <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>65</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920317</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920317</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920318</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920318</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920320</v>
+      </c>
+      <c r="B40" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920320</v>
+      </c>
+      <c r="B41" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920324</v>
+      </c>
+      <c r="B42" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920324</v>
+      </c>
+      <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920326</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>180</v>
+      </c>
+      <c r="E44" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920326</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920327</v>
+      </c>
+      <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>66</v>
+      </c>
+      <c r="G46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920327</v>
+      </c>
+      <c r="B47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920329</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>21330051920329</v>
+      </c>
+      <c r="B49" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>21330051920330</v>
+      </c>
+      <c r="B50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>21330051920330</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G51">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="185">
   <si>
     <t>Materia</t>
   </si>
@@ -215,18 +215,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
@@ -251,57 +251,159 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ATZIRI</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -311,12 +413,6 @@
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>PANZO</t>
   </si>
   <si>
@@ -335,36 +431,18 @@
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>GAMBINO</t>
   </si>
   <si>
@@ -377,9 +455,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>TINOCO</t>
   </si>
   <si>
@@ -392,27 +467,15 @@
     <t>MONTERO</t>
   </si>
   <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>SÁNCHEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -431,57 +494,27 @@
     <t>LIMON</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>VENEGAS</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>RUTH</t>
   </si>
   <si>
     <t>AXEL EDUARDO</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
     <t>CARLOS EMILIO</t>
   </si>
   <si>
     <t>PERLA</t>
   </si>
   <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
     <t>AMY JULIET</t>
   </si>
   <si>
@@ -491,27 +524,12 @@
     <t>YAMILET MONSERRAT</t>
   </si>
   <si>
-    <t>YULIET</t>
-  </si>
-  <si>
     <t>DARLA MARLENE</t>
   </si>
   <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
     <t>DIANA CRISTINA</t>
   </si>
   <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
     <t>ADAL</t>
   </si>
   <si>
@@ -521,12 +539,6 @@
     <t>SAIRA LEILANI</t>
   </si>
   <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -545,18 +557,9 @@
     <t>BRIGITTE</t>
   </si>
   <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
     <t>ANDRIK YOSIMAR</t>
   </si>
   <si>
@@ -564,9 +567,6 @@
   </si>
   <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
   </si>
   <si>
     <t>LIZETH</t>
@@ -1061,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1070,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -1115,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1124,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1138,7 +1138,7 @@
         <v>-1</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1215,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1278,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1292,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1301,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>7</v>
@@ -1346,7 +1346,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1355,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1369,7 +1369,7 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -1378,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -1423,7 +1423,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1446,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1455,7 +1455,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1509,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1523,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -1532,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -1577,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1586,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1600,7 +1600,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -1609,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1654,7 +1654,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1663,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1831,7 +1831,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -1840,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1894,7 +1894,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1908,7 +1908,7 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1962,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1971,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -2039,7 +2039,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2062,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>9</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -2116,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2125,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2139,7 +2139,7 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2148,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -2193,7 +2193,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2216,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2225,7 +2225,7 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2279,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2293,7 +2293,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>8</v>
@@ -2302,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2347,7 +2347,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2356,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2370,7 +2370,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2379,7 +2379,7 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2433,7 +2433,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2447,7 +2447,7 @@
         <v>-1</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2456,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2510,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2524,7 +2524,7 @@
         <v>-1</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -2578,7 +2578,7 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2601,7 +2601,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2610,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -2655,7 +2655,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>9</v>
@@ -2687,7 +2687,7 @@
         <v>8</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2732,7 +2732,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2741,7 +2741,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2755,7 +2755,7 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>9</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2818,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2832,7 +2832,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -2886,7 +2886,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2895,7 +2895,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>-1</v>
@@ -2909,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2972,7 +2972,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -2986,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>-1</v>
@@ -3040,7 +3040,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -3049,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>-1</v>
@@ -3063,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -3072,7 +3072,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>8</v>
@@ -3117,7 +3117,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3126,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3140,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>9</v>
@@ -3149,7 +3149,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -3194,7 +3194,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3203,7 +3203,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3217,7 +3217,7 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>9</v>
@@ -3226,7 +3226,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>8</v>
@@ -3271,7 +3271,7 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3280,7 +3280,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3294,7 +3294,7 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -3303,7 +3303,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G33">
         <v>6</v>
@@ -3348,7 +3348,7 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3357,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>6</v>
@@ -3371,7 +3371,7 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -3425,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3434,7 +3434,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3448,7 +3448,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -3457,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -3502,7 +3502,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3511,7 +3511,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3525,7 +3525,7 @@
         <v>9</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -3534,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>8</v>
@@ -3579,7 +3579,7 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>10</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>8</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>9</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G37">
         <v>7</v>
@@ -3656,7 +3656,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3679,7 +3679,7 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -3688,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -3733,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>-1</v>
@@ -3756,7 +3756,7 @@
         <v>8</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G39">
         <v>8</v>
@@ -3810,7 +3810,7 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>10</v>
@@ -3819,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3833,7 +3833,7 @@
         <v>9</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>9</v>
@@ -3842,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G40">
         <v>-1</v>
@@ -3887,7 +3887,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>9</v>
@@ -3896,7 +3896,7 @@
         <v>10</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y40">
         <v>-1</v>
@@ -3910,7 +3910,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D41">
         <v>9</v>
@@ -3919,7 +3919,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G41">
         <v>7</v>
@@ -3964,7 +3964,7 @@
         <v>7</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>9</v>
@@ -3973,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -3987,7 +3987,7 @@
         <v>9</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>8</v>
@@ -3996,7 +3996,7 @@
         <v>9</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G42">
         <v>-1</v>
@@ -4041,7 +4041,7 @@
         <v>9</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4050,7 +4050,7 @@
         <v>9</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>-1</v>
@@ -4064,7 +4064,7 @@
         <v>9</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>10</v>
@@ -4073,7 +4073,7 @@
         <v>9</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -4118,7 +4118,7 @@
         <v>9</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
         <v>10</v>
@@ -4127,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y43">
         <v>7</v>
@@ -4141,7 +4141,7 @@
         <v>8</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D44">
         <v>10</v>
@@ -4150,7 +4150,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>7</v>
@@ -4195,7 +4195,7 @@
         <v>8</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>10</v>
@@ -4204,7 +4204,7 @@
         <v>10</v>
       </c>
       <c r="X44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y44">
         <v>7</v>
@@ -4227,7 +4227,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <v>-1</v>
@@ -4281,7 +4281,7 @@
         <v>10</v>
       </c>
       <c r="X45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y45">
         <v>-1</v>
@@ -4295,7 +4295,7 @@
         <v>8</v>
       </c>
       <c r="C46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D46">
         <v>9</v>
@@ -4304,7 +4304,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <v>7</v>
@@ -4349,7 +4349,7 @@
         <v>8</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V46">
         <v>9</v>
@@ -4358,7 +4358,7 @@
         <v>10</v>
       </c>
       <c r="X46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y46">
         <v>7</v>
@@ -4372,7 +4372,7 @@
         <v>7</v>
       </c>
       <c r="C47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D47">
         <v>10</v>
@@ -4381,7 +4381,7 @@
         <v>9</v>
       </c>
       <c r="F47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G47">
         <v>8</v>
@@ -4426,7 +4426,7 @@
         <v>7</v>
       </c>
       <c r="U47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V47">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>9</v>
       </c>
       <c r="X47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y47">
         <v>8</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -4503,27 +4503,30 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>4.55</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4532,27 +4535,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.9</v>
+      </c>
       <c r="I3">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4561,30 +4567,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>63.64</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>31.82</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4593,25 +4599,25 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>84.09</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>15.91</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4685,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4720,16 +4726,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4740,13 +4746,13 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
@@ -4754,39 +4760,39 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920289</v>
+        <v>21330051920290</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920290</v>
+        <v>21330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -4794,119 +4800,119 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920290</v>
+        <v>21330051920296</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920290</v>
+        <v>21330051920297</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920291</v>
+        <v>21330051920298</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920291</v>
+        <v>21330051920298</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920292</v>
+        <v>21330051920298</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920292</v>
+        <v>21330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>66</v>
@@ -4914,119 +4920,119 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920293</v>
+        <v>21330051920299</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920293</v>
+        <v>21330051920299</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920293</v>
+        <v>21330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920294</v>
+        <v>21330051920299</v>
       </c>
       <c r="B15" t="s">
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920294</v>
+        <v>21330051920337</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920295</v>
+        <v>21330051920337</v>
       </c>
       <c r="B17" t="s">
         <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
@@ -5034,39 +5040,39 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920295</v>
+        <v>21330051920303</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920296</v>
+        <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
@@ -5074,19 +5080,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920296</v>
+        <v>21330051920306</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
@@ -5094,39 +5100,39 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920296</v>
+        <v>20330051920235</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920297</v>
+        <v>20330051920235</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
         <v>65</v>
@@ -5134,79 +5140,79 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920297</v>
+        <v>21330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920297</v>
+        <v>21330051920311</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920298</v>
+        <v>21330051920312</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920298</v>
+        <v>21330051920319</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>65</v>
@@ -5214,1722 +5220,102 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920298</v>
+        <v>21330051920321</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920298</v>
+        <v>21330051920323</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920299</v>
+        <v>21330051920328</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920299</v>
+        <v>21330051920328</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920299</v>
+        <v>21330051920328</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920299</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" t="s">
-        <v>152</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920337</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920337</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920337</v>
-      </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920300</v>
-      </c>
-      <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" t="s">
-        <v>154</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920300</v>
-      </c>
-      <c r="B37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920301</v>
-      </c>
-      <c r="B38" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920301</v>
-      </c>
-      <c r="B39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" t="s">
-        <v>155</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920302</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" t="s">
-        <v>156</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920302</v>
-      </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" t="s">
-        <v>156</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920303</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" t="s">
-        <v>157</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920303</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" t="s">
-        <v>157</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920303</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920304</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" t="s">
-        <v>158</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920304</v>
-      </c>
-      <c r="B46" t="s">
-        <v>89</v>
-      </c>
-      <c r="C46" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" t="s">
-        <v>158</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920305</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920305</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920305</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49" t="s">
-        <v>159</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920306</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" t="s">
-        <v>160</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920306</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920306</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>105</v>
-      </c>
-      <c r="D52" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920235</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
-        <v>125</v>
-      </c>
-      <c r="D53" t="s">
-        <v>161</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920235</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" t="s">
-        <v>125</v>
-      </c>
-      <c r="D54" t="s">
-        <v>161</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920235</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" t="s">
-        <v>125</v>
-      </c>
-      <c r="D55" t="s">
-        <v>161</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920235</v>
-      </c>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" t="s">
-        <v>161</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920307</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920307</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="s">
-        <v>126</v>
-      </c>
-      <c r="D58" t="s">
-        <v>162</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920308</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>127</v>
-      </c>
-      <c r="D59" t="s">
-        <v>163</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920308</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" t="s">
-        <v>127</v>
-      </c>
-      <c r="D60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920308</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
-      </c>
-      <c r="C61" t="s">
-        <v>127</v>
-      </c>
-      <c r="D61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920309</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" t="s">
-        <v>99</v>
-      </c>
-      <c r="D62" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920309</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>99</v>
-      </c>
-      <c r="D63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920090</v>
-      </c>
-      <c r="B64" t="s">
-        <v>95</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64" t="s">
-        <v>165</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920090</v>
-      </c>
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" t="s">
-        <v>165</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920310</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>129</v>
-      </c>
-      <c r="D66" t="s">
-        <v>166</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920310</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" t="s">
-        <v>166</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920311</v>
-      </c>
-      <c r="B68" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68" t="s">
-        <v>167</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920311</v>
-      </c>
-      <c r="B69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" t="s">
-        <v>130</v>
-      </c>
-      <c r="D69" t="s">
-        <v>167</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920311</v>
-      </c>
-      <c r="B70" t="s">
-        <v>97</v>
-      </c>
-      <c r="C70" t="s">
-        <v>130</v>
-      </c>
-      <c r="D70" t="s">
-        <v>167</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920312</v>
-      </c>
-      <c r="B71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" t="s">
-        <v>125</v>
-      </c>
-      <c r="D71" t="s">
-        <v>168</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920312</v>
-      </c>
-      <c r="B72" t="s">
-        <v>98</v>
-      </c>
-      <c r="C72" t="s">
-        <v>125</v>
-      </c>
-      <c r="D72" t="s">
-        <v>168</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920312</v>
-      </c>
-      <c r="B73" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" t="s">
-        <v>125</v>
-      </c>
-      <c r="D73" t="s">
-        <v>168</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920313</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>94</v>
-      </c>
-      <c r="D74" t="s">
-        <v>169</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920313</v>
-      </c>
-      <c r="B75" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" t="s">
-        <v>94</v>
-      </c>
-      <c r="D75" t="s">
-        <v>169</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920314</v>
-      </c>
-      <c r="B76" t="s">
-        <v>100</v>
-      </c>
-      <c r="C76" t="s">
-        <v>93</v>
-      </c>
-      <c r="D76" t="s">
-        <v>170</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920314</v>
-      </c>
-      <c r="B77" t="s">
-        <v>100</v>
-      </c>
-      <c r="C77" t="s">
-        <v>93</v>
-      </c>
-      <c r="D77" t="s">
-        <v>170</v>
-      </c>
-      <c r="E77" t="s">
-        <v>6</v>
-      </c>
-      <c r="F77" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920172</v>
-      </c>
-      <c r="B78" t="s">
-        <v>101</v>
-      </c>
-      <c r="C78" t="s">
-        <v>131</v>
-      </c>
-      <c r="D78" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920172</v>
-      </c>
-      <c r="B79" t="s">
-        <v>101</v>
-      </c>
-      <c r="C79" t="s">
-        <v>131</v>
-      </c>
-      <c r="D79" t="s">
-        <v>171</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920315</v>
-      </c>
-      <c r="B80" t="s">
-        <v>102</v>
-      </c>
-      <c r="C80" t="s">
-        <v>132</v>
-      </c>
-      <c r="D80" t="s">
-        <v>172</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920315</v>
-      </c>
-      <c r="B81" t="s">
-        <v>102</v>
-      </c>
-      <c r="C81" t="s">
-        <v>132</v>
-      </c>
-      <c r="D81" t="s">
-        <v>172</v>
-      </c>
-      <c r="E81" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920316</v>
-      </c>
-      <c r="B82" t="s">
-        <v>103</v>
-      </c>
-      <c r="C82" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" t="s">
-        <v>169</v>
-      </c>
-      <c r="E82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920316</v>
-      </c>
-      <c r="B83" t="s">
-        <v>103</v>
-      </c>
-      <c r="C83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" t="s">
-        <v>169</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920317</v>
-      </c>
-      <c r="B84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C84" t="s">
-        <v>134</v>
-      </c>
-      <c r="D84" t="s">
-        <v>173</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920317</v>
-      </c>
-      <c r="B85" t="s">
-        <v>104</v>
-      </c>
-      <c r="C85" t="s">
-        <v>134</v>
-      </c>
-      <c r="D85" t="s">
-        <v>173</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920318</v>
-      </c>
-      <c r="B86" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86" t="s">
-        <v>135</v>
-      </c>
-      <c r="D86" t="s">
-        <v>174</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920318</v>
-      </c>
-      <c r="B87" t="s">
-        <v>105</v>
-      </c>
-      <c r="C87" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" t="s">
-        <v>174</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920319</v>
-      </c>
-      <c r="B88" t="s">
-        <v>105</v>
-      </c>
-      <c r="C88" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
-        <v>175</v>
-      </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920319</v>
-      </c>
-      <c r="B89" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
-        <v>175</v>
-      </c>
-      <c r="E89" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920319</v>
-      </c>
-      <c r="B90" t="s">
-        <v>105</v>
-      </c>
-      <c r="C90" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
-        <v>175</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920320</v>
-      </c>
-      <c r="B91" t="s">
-        <v>106</v>
-      </c>
-      <c r="C91" t="s">
-        <v>136</v>
-      </c>
-      <c r="D91" t="s">
-        <v>176</v>
-      </c>
-      <c r="E91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920320</v>
-      </c>
-      <c r="B92" t="s">
-        <v>106</v>
-      </c>
-      <c r="C92" t="s">
-        <v>136</v>
-      </c>
-      <c r="D92" t="s">
-        <v>176</v>
-      </c>
-      <c r="E92" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920321</v>
-      </c>
-      <c r="B93" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93" t="s">
-        <v>177</v>
-      </c>
-      <c r="E93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920321</v>
-      </c>
-      <c r="B94" t="s">
-        <v>106</v>
-      </c>
-      <c r="C94" t="s">
-        <v>137</v>
-      </c>
-      <c r="D94" t="s">
-        <v>177</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920321</v>
-      </c>
-      <c r="B95" t="s">
-        <v>106</v>
-      </c>
-      <c r="C95" t="s">
-        <v>137</v>
-      </c>
-      <c r="D95" t="s">
-        <v>177</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920323</v>
-      </c>
-      <c r="B96" t="s">
-        <v>107</v>
-      </c>
-      <c r="C96" t="s">
-        <v>125</v>
-      </c>
-      <c r="D96" t="s">
-        <v>178</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920323</v>
-      </c>
-      <c r="B97" t="s">
-        <v>107</v>
-      </c>
-      <c r="C97" t="s">
-        <v>125</v>
-      </c>
-      <c r="D97" t="s">
-        <v>178</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920323</v>
-      </c>
-      <c r="B98" t="s">
-        <v>107</v>
-      </c>
-      <c r="C98" t="s">
-        <v>125</v>
-      </c>
-      <c r="D98" t="s">
-        <v>178</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920324</v>
-      </c>
-      <c r="B99" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" t="s">
-        <v>138</v>
-      </c>
-      <c r="D99" t="s">
-        <v>179</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920324</v>
-      </c>
-      <c r="B100" t="s">
-        <v>108</v>
-      </c>
-      <c r="C100" t="s">
-        <v>138</v>
-      </c>
-      <c r="D100" t="s">
-        <v>179</v>
-      </c>
-      <c r="E100" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920326</v>
-      </c>
-      <c r="B101" t="s">
-        <v>109</v>
-      </c>
-      <c r="C101" t="s">
-        <v>105</v>
-      </c>
-      <c r="D101" t="s">
-        <v>180</v>
-      </c>
-      <c r="E101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920326</v>
-      </c>
-      <c r="B102" t="s">
-        <v>109</v>
-      </c>
-      <c r="C102" t="s">
-        <v>105</v>
-      </c>
-      <c r="D102" t="s">
-        <v>180</v>
-      </c>
-      <c r="E102" t="s">
-        <v>6</v>
-      </c>
-      <c r="F102" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920327</v>
-      </c>
-      <c r="B103" t="s">
-        <v>110</v>
-      </c>
-      <c r="C103" t="s">
-        <v>92</v>
-      </c>
-      <c r="D103" t="s">
-        <v>181</v>
-      </c>
-      <c r="E103" t="s">
-        <v>9</v>
-      </c>
-      <c r="F103" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920327</v>
-      </c>
-      <c r="B104" t="s">
-        <v>110</v>
-      </c>
-      <c r="C104" t="s">
-        <v>92</v>
-      </c>
-      <c r="D104" t="s">
-        <v>181</v>
-      </c>
-      <c r="E104" t="s">
-        <v>6</v>
-      </c>
-      <c r="F104" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920328</v>
-      </c>
-      <c r="B105" t="s">
-        <v>111</v>
-      </c>
-      <c r="C105" t="s">
-        <v>139</v>
-      </c>
-      <c r="D105" t="s">
-        <v>182</v>
-      </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920328</v>
-      </c>
-      <c r="B106" t="s">
-        <v>111</v>
-      </c>
-      <c r="C106" t="s">
-        <v>139</v>
-      </c>
-      <c r="D106" t="s">
-        <v>182</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920328</v>
-      </c>
-      <c r="B107" t="s">
-        <v>111</v>
-      </c>
-      <c r="C107" t="s">
-        <v>139</v>
-      </c>
-      <c r="D107" t="s">
-        <v>182</v>
-      </c>
-      <c r="E107" t="s">
-        <v>5</v>
-      </c>
-      <c r="F107" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920328</v>
-      </c>
-      <c r="B108" t="s">
-        <v>111</v>
-      </c>
-      <c r="C108" t="s">
-        <v>139</v>
-      </c>
-      <c r="D108" t="s">
-        <v>182</v>
-      </c>
-      <c r="E108" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920329</v>
-      </c>
-      <c r="B109" t="s">
-        <v>112</v>
-      </c>
-      <c r="C109" t="s">
-        <v>140</v>
-      </c>
-      <c r="D109" t="s">
-        <v>183</v>
-      </c>
-      <c r="E109" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920329</v>
-      </c>
-      <c r="B110" t="s">
-        <v>112</v>
-      </c>
-      <c r="C110" t="s">
-        <v>140</v>
-      </c>
-      <c r="D110" t="s">
-        <v>183</v>
-      </c>
-      <c r="E110" t="s">
-        <v>6</v>
-      </c>
-      <c r="F110" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920330</v>
-      </c>
-      <c r="B111" t="s">
-        <v>113</v>
-      </c>
-      <c r="C111" t="s">
-        <v>141</v>
-      </c>
-      <c r="D111" t="s">
-        <v>184</v>
-      </c>
-      <c r="E111" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920330</v>
-      </c>
-      <c r="B112" t="s">
-        <v>113</v>
-      </c>
-      <c r="C112" t="s">
-        <v>141</v>
-      </c>
-      <c r="D112" t="s">
-        <v>184</v>
-      </c>
-      <c r="E112" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -6968,13 +5354,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -6985,13 +5371,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -6999,138 +5385,138 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920235</v>
+        <v>21330051920328</v>
       </c>
       <c r="B4" t="s">
         <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920328</v>
+        <v>21330051920289</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920289</v>
+        <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920290</v>
+        <v>20330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920293</v>
+        <v>21330051920290</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920296</v>
+        <v>21330051920293</v>
       </c>
       <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
         <v>82</v>
       </c>
-      <c r="C9" t="s">
-        <v>119</v>
-      </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920297</v>
+        <v>21330051920296</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920337</v>
+        <v>21330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7138,16 +5524,16 @@
         <v>21330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7155,16 +5541,16 @@
         <v>21330051920305</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7172,16 +5558,16 @@
         <v>21330051920306</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7189,16 +5575,16 @@
         <v>21330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7206,16 +5592,16 @@
         <v>21330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7223,16 +5609,16 @@
         <v>21330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7240,16 +5626,16 @@
         <v>21330051920319</v>
       </c>
       <c r="B18" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7257,16 +5643,16 @@
         <v>21330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7274,16 +5660,16 @@
         <v>21330051920323</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7291,16 +5677,16 @@
         <v>21330051920291</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7308,16 +5694,16 @@
         <v>21330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7325,16 +5711,16 @@
         <v>21330051920294</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7342,16 +5728,16 @@
         <v>21330051920295</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7359,16 +5745,16 @@
         <v>21330051920300</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7376,16 +5762,16 @@
         <v>21330051920301</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7393,16 +5779,16 @@
         <v>21330051920302</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7410,16 +5796,16 @@
         <v>21330051920304</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7427,16 +5813,16 @@
         <v>21330051920307</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7444,16 +5830,16 @@
         <v>21330051920309</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7461,16 +5847,16 @@
         <v>21330051920090</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7478,16 +5864,16 @@
         <v>21330051920310</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7495,16 +5881,16 @@
         <v>21330051920313</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7512,16 +5898,16 @@
         <v>21330051920314</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7529,16 +5915,16 @@
         <v>21330051920172</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7546,16 +5932,16 @@
         <v>21330051920315</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7563,16 +5949,16 @@
         <v>21330051920316</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7580,16 +5966,16 @@
         <v>21330051920317</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -7597,16 +5983,16 @@
         <v>21330051920318</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7614,16 +6000,16 @@
         <v>21330051920320</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -7631,16 +6017,16 @@
         <v>21330051920324</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7648,16 +6034,16 @@
         <v>21330051920326</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -7665,16 +6051,16 @@
         <v>21330051920327</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -7682,16 +6068,16 @@
         <v>21330051920329</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7699,16 +6085,16 @@
         <v>21330051920330</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7718,7 +6104,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7750,19 +6136,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920291</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
@@ -7773,22 +6159,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920291</v>
+        <v>21330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -7796,22 +6182,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920292</v>
+        <v>21330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -7819,19 +6205,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920292</v>
+        <v>21330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -7842,19 +6228,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920294</v>
+        <v>20330051920235</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -7865,19 +6251,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920294</v>
+        <v>20330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -7888,22 +6274,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920295</v>
+        <v>21330051920290</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -7911,19 +6297,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920295</v>
+        <v>21330051920293</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
@@ -7934,22 +6320,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920300</v>
+        <v>21330051920296</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -7957,22 +6343,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920300</v>
+        <v>21330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -7980,22 +6366,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920301</v>
+        <v>21330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -8003,19 +6389,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920301</v>
+        <v>21330051920305</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -8026,19 +6412,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920302</v>
+        <v>21330051920306</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>66</v>
@@ -8049,19 +6435,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920302</v>
+        <v>21330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>65</v>
@@ -8072,22 +6458,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920304</v>
+        <v>21330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -8095,19 +6481,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920304</v>
+        <v>21330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
@@ -8118,22 +6504,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920307</v>
+        <v>21330051920319</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -8141,19 +6527,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920307</v>
+        <v>21330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
@@ -8164,737 +6550,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920309</v>
+        <v>21330051920323</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920309</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920090</v>
-      </c>
-      <c r="B22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920090</v>
-      </c>
-      <c r="B23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>165</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920310</v>
-      </c>
-      <c r="B24" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920310</v>
-      </c>
-      <c r="B25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" t="s">
-        <v>166</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920313</v>
-      </c>
-      <c r="B26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920313</v>
-      </c>
-      <c r="B27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920314</v>
-      </c>
-      <c r="B28" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>170</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920314</v>
-      </c>
-      <c r="B29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>170</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920172</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920172</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920315</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920315</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920316</v>
-      </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" t="s">
-        <v>169</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920316</v>
-      </c>
-      <c r="B35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920317</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" t="s">
-        <v>173</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920317</v>
-      </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" t="s">
-        <v>173</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920318</v>
-      </c>
-      <c r="B38" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920318</v>
-      </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>65</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920320</v>
-      </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" t="s">
-        <v>136</v>
-      </c>
-      <c r="D40" t="s">
-        <v>176</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920320</v>
-      </c>
-      <c r="B41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" t="s">
-        <v>136</v>
-      </c>
-      <c r="D41" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920324</v>
-      </c>
-      <c r="B42" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920324</v>
-      </c>
-      <c r="B43" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43" t="s">
-        <v>179</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920326</v>
-      </c>
-      <c r="B44" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
-        <v>180</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>66</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920326</v>
-      </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>180</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920327</v>
-      </c>
-      <c r="B46" t="s">
-        <v>110</v>
-      </c>
-      <c r="C46" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46" t="s">
-        <v>181</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920327</v>
-      </c>
-      <c r="B47" t="s">
-        <v>110</v>
-      </c>
-      <c r="C47" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>65</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920329</v>
-      </c>
-      <c r="B48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" t="s">
-        <v>183</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920329</v>
-      </c>
-      <c r="B49" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" t="s">
-        <v>140</v>
-      </c>
-      <c r="D49" t="s">
-        <v>183</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920330</v>
-      </c>
-      <c r="B50" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D50" t="s">
-        <v>184</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920330</v>
-      </c>
-      <c r="B51" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" t="s">
-        <v>141</v>
-      </c>
-      <c r="D51" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="185">
   <si>
     <t>Materia</t>
   </si>
@@ -215,21 +215,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
@@ -248,43 +248,133 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
   <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>JUSTO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MOTA</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
   </si>
   <si>
     <t>REYES</t>
@@ -293,271 +383,181 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
   </si>
   <si>
     <t>NEGRETE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>ZARATE</t>
   </si>
   <si>
     <t>CERON</t>
   </si>
   <si>
+    <t>SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VILLASEÑOR</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
   </si>
   <si>
     <t>JAZMIN</t>
   </si>
   <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
     <t>ATZIRI</t>
   </si>
   <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
   </si>
   <si>
     <t>YULIET</t>
   </si>
   <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
     <t>MARIA MICHELLE</t>
   </si>
   <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
+    <t>DIANA CRISTINA</t>
   </si>
   <si>
     <t>ANGEL DIEGO</t>
   </si>
   <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>SAIRA LEILANI</t>
+  </si>
+  <si>
     <t>MONICA AIME</t>
   </si>
   <si>
     <t>ARACELY</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GONZALO</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
+    <t>REBECA</t>
+  </si>
+  <si>
+    <t>BRIGITTE</t>
+  </si>
+  <si>
     <t>SAYURI BETSABE</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
     <t>ANA LAURA</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ADAL</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
   </si>
   <si>
     <t>ANDRIK YOSIMAR</t>
@@ -1079,10 +1079,10 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1115,10 +1115,10 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1127,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1156,7 +1156,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1168,7 +1168,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1204,7 +1204,7 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1227,16 +1227,16 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1245,7 +1245,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1272,7 +1272,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1281,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1310,10 +1310,10 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1387,10 +1387,10 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1399,7 +1399,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1426,7 +1426,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1458,16 +1458,16 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1476,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1535,16 +1535,16 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1553,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1580,7 +1580,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1589,7 +1589,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1618,10 +1618,10 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1654,10 +1654,10 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1666,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1677,10 +1677,10 @@
         <v>-1</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1695,7 +1695,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1707,7 +1707,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1731,10 +1731,10 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1754,10 +1754,10 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1772,7 +1772,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1784,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1808,10 +1808,10 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1820,7 +1820,7 @@
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1849,10 +1849,10 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1861,7 +1861,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1897,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1926,10 +1926,10 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1938,7 +1938,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1974,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1997,16 +1997,16 @@
         <v>-1</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2015,7 +2015,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2051,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2080,10 +2080,10 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2092,7 +2092,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2116,10 +2116,10 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2128,7 +2128,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2157,10 +2157,10 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2169,7 +2169,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2193,7 +2193,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2205,7 +2205,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2228,16 +2228,16 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2246,7 +2246,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2282,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2311,10 +2311,10 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2323,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2359,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2382,16 +2382,16 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2400,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2436,7 +2436,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2465,10 +2465,10 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2477,7 +2477,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2536,16 +2536,16 @@
         <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2554,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2578,10 +2578,10 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2590,7 +2590,7 @@
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2619,10 +2619,10 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2631,7 +2631,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2655,10 +2655,10 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2667,7 +2667,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2696,10 +2696,10 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2708,7 +2708,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2732,10 +2732,10 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2744,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2773,10 +2773,10 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2785,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2821,7 +2821,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2844,16 +2844,16 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2862,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2898,7 +2898,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2921,16 +2921,16 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2939,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2975,7 +2975,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2998,16 +2998,16 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3016,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3043,7 +3043,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3052,7 +3052,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3081,10 +3081,10 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3093,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3129,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3158,10 +3158,10 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3170,7 +3170,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3206,7 +3206,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3235,10 +3235,10 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3247,7 +3247,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3274,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3283,7 +3283,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3312,10 +3312,10 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3324,7 +3324,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3360,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3389,10 +3389,10 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3401,7 +3401,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3428,7 +3428,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3437,7 +3437,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3466,10 +3466,10 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3478,7 +3478,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3502,7 +3502,7 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3514,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3543,10 +3543,10 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3555,7 +3555,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3591,7 +3591,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3620,10 +3620,10 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3632,7 +3632,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3656,7 +3656,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3668,7 +3668,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3691,16 +3691,16 @@
         <v>7</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3709,7 +3709,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3745,7 +3745,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3774,10 +3774,10 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3786,7 +3786,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3822,7 +3822,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3845,16 +3845,16 @@
         <v>10</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -3863,7 +3863,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3899,7 +3899,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3928,10 +3928,10 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -3940,7 +3940,7 @@
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3967,7 +3967,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -3999,16 +3999,16 @@
         <v>8</v>
       </c>
       <c r="G42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -4017,7 +4017,7 @@
         <v>-1</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4082,10 +4082,10 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
         <v>-1</v>
@@ -4094,7 +4094,7 @@
         <v>-1</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4130,7 +4130,7 @@
         <v>10</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4159,10 +4159,10 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
         <v>-1</v>
@@ -4171,7 +4171,7 @@
         <v>-1</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4218,7 +4218,7 @@
         <v>-1</v>
       </c>
       <c r="C45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7</v>
@@ -4230,13 +4230,13 @@
         <v>8</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H45">
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J45">
         <v>-1</v>
@@ -4248,7 +4248,7 @@
         <v>-1</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4272,7 +4272,7 @@
         <v>-1</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V45">
         <v>7</v>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4313,10 +4313,10 @@
         <v>-1</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K46">
         <v>-1</v>
@@ -4325,7 +4325,7 @@
         <v>-1</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4349,7 +4349,7 @@
         <v>8</v>
       </c>
       <c r="U46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V46">
         <v>9</v>
@@ -4361,7 +4361,7 @@
         <v>10</v>
       </c>
       <c r="Y46">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4390,7 +4390,7 @@
         <v>-1</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J47">
         <v>-1</v>
@@ -4402,7 +4402,7 @@
         <v>-1</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4426,7 +4426,7 @@
         <v>7</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V47">
         <v>10</v>
@@ -4438,7 +4438,7 @@
         <v>10</v>
       </c>
       <c r="Y47">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
@@ -4503,30 +4503,30 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>63.64</v>
+        <v>84.09</v>
       </c>
       <c r="G2">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>31.82</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4535,30 +4535,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>84.09</v>
+        <v>90.91</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>15.91</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4567,30 +4567,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>95.45</v>
+      </c>
+      <c r="G4">
+        <v>4.55</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>90.91</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4599,30 +4599,30 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4631,25 +4631,25 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4691,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4726,16 +4726,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4746,33 +4746,33 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920290</v>
+        <v>21330051920297</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920293</v>
+        <v>21330051920298</v>
       </c>
       <c r="B5" t="s">
         <v>77</v>
@@ -4789,30 +4789,30 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920296</v>
+        <v>21330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -4820,19 +4820,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920297</v>
+        <v>21330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
@@ -4840,481 +4840,101 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920298</v>
+        <v>21330051920299</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920298</v>
+        <v>21330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920298</v>
+        <v>21330051920306</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920298</v>
+        <v>20330051920235</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
         <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920299</v>
+        <v>21330051920328</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920299</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920299</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920299</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920337</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920337</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920303</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920305</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920306</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920235</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920235</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920308</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920311</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920312</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920319</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920321</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920323</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920328</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920328</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920328</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5351,70 +4971,70 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920298</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920299</v>
+        <v>21330051920298</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920328</v>
+        <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920289</v>
+        <v>21330051920297</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5422,47 +5042,47 @@
         <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920235</v>
+        <v>21330051920306</v>
       </c>
       <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
       </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920290</v>
+        <v>20330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
         <v>93</v>
-      </c>
-      <c r="D8" t="s">
-        <v>103</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5470,16 +5090,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920293</v>
+        <v>21330051920328</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5487,200 +5107,200 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920296</v>
+        <v>21330051920290</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920297</v>
+        <v>21330051920291</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920303</v>
+        <v>21330051920292</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920305</v>
+        <v>21330051920293</v>
       </c>
       <c r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920306</v>
+        <v>21330051920294</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920308</v>
+        <v>21330051920295</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920311</v>
+        <v>21330051920296</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920312</v>
+        <v>21330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920319</v>
+        <v>21330051920301</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920321</v>
+        <v>21330051920302</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920323</v>
+        <v>21330051920303</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920291</v>
+        <v>21330051920304</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -5691,13 +5311,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920292</v>
+        <v>21330051920305</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5708,13 +5328,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920294</v>
+        <v>21330051920307</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -5725,13 +5345,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920295</v>
+        <v>21330051920308</v>
       </c>
       <c r="B24" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5742,13 +5362,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920300</v>
+        <v>21330051920309</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5759,13 +5379,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920301</v>
+        <v>21330051920090</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5776,13 +5396,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920302</v>
+        <v>21330051920310</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
         <v>167</v>
@@ -5793,13 +5413,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920304</v>
+        <v>21330051920311</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5810,13 +5430,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920307</v>
+        <v>21330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5827,13 +5447,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920309</v>
+        <v>21330051920313</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5844,13 +5464,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920090</v>
+        <v>21330051920314</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5861,13 +5481,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920310</v>
+        <v>21330051920172</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5878,13 +5498,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920313</v>
+        <v>21330051920315</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
         <v>173</v>
@@ -5895,16 +5515,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920314</v>
+        <v>21330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5912,16 +5532,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920172</v>
+        <v>21330051920317</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5929,16 +5549,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920315</v>
+        <v>21330051920318</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5946,16 +5566,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920316</v>
+        <v>21330051920319</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5963,13 +5583,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920317</v>
+        <v>21330051920320</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -5980,13 +5600,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920318</v>
+        <v>21330051920321</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -5997,13 +5617,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920320</v>
+        <v>21330051920323</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6017,10 +5637,10 @@
         <v>21330051920324</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -6034,10 +5654,10 @@
         <v>21330051920326</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -6051,10 +5671,10 @@
         <v>21330051920327</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -6068,10 +5688,10 @@
         <v>21330051920329</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -6085,10 +5705,10 @@
         <v>21330051920330</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -6104,7 +5724,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6142,16 +5762,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6165,16 +5785,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6182,22 +5802,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920337</v>
+        <v>21330051920299</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6205,22 +5825,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920337</v>
+        <v>21330051920299</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6228,19 +5848,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920235</v>
+        <v>21330051920337</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -6251,42 +5871,42 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920235</v>
+        <v>21330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920290</v>
+        <v>21330051920297</v>
       </c>
       <c r="B8" t="s">
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
@@ -6297,19 +5917,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920293</v>
+        <v>21330051920306</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
@@ -6320,19 +5940,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920296</v>
+        <v>20330051920235</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
@@ -6343,231 +5963,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920297</v>
+        <v>21330051920328</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920303</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920305</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920306</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920308</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920311</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920312</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920319</v>
-      </c>
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920321</v>
-      </c>
-      <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920323</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="185">
   <si>
     <t>Materia</t>
   </si>
@@ -248,6 +248,27 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -257,33 +278,198 @@
     <t>FRANCO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>ATZIRI</t>
+  </si>
+  <si>
     <t>EDNA</t>
   </si>
   <si>
@@ -296,277 +482,91 @@
     <t>CRISTOPHER</t>
   </si>
   <si>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
     <t>ANETTE JOCELYN</t>
   </si>
   <si>
     <t>JOSE RAFAEL</t>
   </si>
   <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>SAIRA LEILANI</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GONZALO</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
+    <t>REBECA</t>
+  </si>
+  <si>
+    <t>BRIGITTE</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ANDRIK YOSIMAR</t>
+  </si>
+  <si>
+    <t>IVANNA DANIELA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
     <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>ADAL</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
   <si>
     <t>LIZETH</t>
@@ -1076,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -1085,10 +1085,10 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1112,7 +1112,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1121,10 +1121,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1135,7 +1135,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1147,13 +1147,13 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -1162,10 +1162,10 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1198,10 +1198,10 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1230,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1239,10 +1239,10 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1275,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1307,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -1316,10 +1316,10 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1352,10 +1352,10 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1384,7 +1384,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1393,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1461,7 +1461,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1470,10 +1470,10 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1509,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1538,7 +1538,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1547,10 +1547,10 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1583,10 +1583,10 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1615,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -1624,10 +1624,10 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1674,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1686,25 +1686,25 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1737,10 +1737,10 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1751,7 +1751,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1763,25 +1763,25 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>3</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1805,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1814,10 +1814,10 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1828,7 +1828,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1846,7 +1846,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -1855,10 +1855,10 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1882,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1891,10 +1891,10 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1923,7 +1923,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -1932,10 +1932,10 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1994,13 +1994,13 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -2009,10 +2009,10 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -2045,10 +2045,10 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2077,7 +2077,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -2086,10 +2086,10 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2125,7 +2125,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2154,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -2163,10 +2163,10 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2231,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -2240,10 +2240,10 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2308,7 +2308,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2317,10 +2317,10 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>9</v>
@@ -2356,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2385,7 +2385,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -2394,10 +2394,10 @@
         <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2430,10 +2430,10 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2444,7 +2444,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -2471,10 +2471,10 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2498,7 +2498,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2507,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2521,7 +2521,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2539,7 +2539,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2548,10 +2548,10 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2575,7 +2575,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2616,7 +2616,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2625,10 +2625,10 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2661,10 +2661,10 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2693,7 +2693,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2702,10 +2702,10 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2738,10 +2738,10 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -2779,10 +2779,10 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2815,7 +2815,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2847,7 +2847,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2856,10 +2856,10 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>8</v>
@@ -2883,7 +2883,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2892,10 +2892,10 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2924,7 +2924,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2933,10 +2933,10 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -2960,7 +2960,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2969,10 +2969,10 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3001,7 +3001,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -3010,10 +3010,10 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -3037,7 +3037,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3049,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3078,7 +3078,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -3087,10 +3087,10 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3155,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -3164,10 +3164,10 @@
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3232,7 +3232,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -3241,10 +3241,10 @@
         <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3277,10 +3277,10 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3309,7 +3309,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3318,10 +3318,10 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -3386,7 +3386,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>8</v>
@@ -3395,10 +3395,10 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>9</v>
@@ -3422,7 +3422,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3463,7 +3463,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3472,10 +3472,10 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3511,7 +3511,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3540,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3549,10 +3549,10 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>7</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
         <v>10</v>
@@ -3626,10 +3626,10 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3694,7 +3694,7 @@
         <v>5</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>7</v>
@@ -3703,10 +3703,10 @@
         <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
         <v>9</v>
@@ -3730,7 +3730,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3771,7 +3771,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -3780,10 +3780,10 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <v>9</v>
@@ -3848,7 +3848,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -3857,10 +3857,10 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
         <v>10</v>
@@ -3925,7 +3925,7 @@
         <v>7</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -3934,10 +3934,10 @@
         <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>6</v>
@@ -3961,7 +3961,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>9</v>
@@ -3970,10 +3970,10 @@
         <v>7</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -4002,7 +4002,7 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>7</v>
@@ -4011,10 +4011,10 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
         <v>9</v>
@@ -4038,7 +4038,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U42">
         <v>8</v>
@@ -4079,7 +4079,7 @@
         <v>7</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>9</v>
@@ -4088,10 +4088,10 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M43">
         <v>10</v>
@@ -4115,7 +4115,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U43">
         <v>10</v>
@@ -4156,7 +4156,7 @@
         <v>7</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -4165,10 +4165,10 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M44">
         <v>7</v>
@@ -4192,7 +4192,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -4233,7 +4233,7 @@
         <v>5</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -4242,10 +4242,10 @@
         <v>-1</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M45">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U45">
         <v>7</v>
@@ -4310,7 +4310,7 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I46">
         <v>9</v>
@@ -4319,10 +4319,10 @@
         <v>9</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M46">
         <v>10</v>
@@ -4346,7 +4346,7 @@
         <v>-1</v>
       </c>
       <c r="T46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U46">
         <v>9</v>
@@ -4387,7 +4387,7 @@
         <v>8</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>7</v>
@@ -4396,10 +4396,10 @@
         <v>-1</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M47">
         <v>10</v>
@@ -4423,7 +4423,7 @@
         <v>-1</v>
       </c>
       <c r="T47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U47">
         <v>8</v>
@@ -4435,7 +4435,7 @@
         <v>9</v>
       </c>
       <c r="X47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y47">
         <v>9</v>
@@ -4503,25 +4503,25 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>84.09</v>
+        <v>86.36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4535,25 +4535,25 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>90.91</v>
+        <v>88.64</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>11.36</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4691,7 +4691,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4716,226 +4716,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920289</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920289</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920297</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920298</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920298</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920299</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920306</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920235</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920328</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4977,143 +4757,143 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920298</v>
+        <v>21330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920299</v>
+        <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920297</v>
+        <v>21330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920337</v>
+        <v>21330051920293</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920306</v>
+        <v>21330051920294</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920235</v>
+        <v>21330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920328</v>
+        <v>21330051920296</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920290</v>
+        <v>21330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>150</v>
@@ -5124,13 +4904,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920291</v>
+        <v>21330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
         <v>151</v>
@@ -5141,13 +4921,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920292</v>
+        <v>21330051920299</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
         <v>152</v>
@@ -5158,13 +4938,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920293</v>
+        <v>21330051920337</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>153</v>
@@ -5175,13 +4955,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920294</v>
+        <v>21330051920300</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
         <v>154</v>
@@ -5192,13 +4972,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920295</v>
+        <v>21330051920301</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>155</v>
@@ -5209,13 +4989,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920296</v>
+        <v>21330051920302</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -5226,13 +5006,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920300</v>
+        <v>21330051920303</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -5243,13 +5023,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920301</v>
+        <v>21330051920304</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>158</v>
@@ -5260,13 +5040,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920302</v>
+        <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>159</v>
@@ -5277,13 +5057,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920303</v>
+        <v>21330051920306</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
         <v>160</v>
@@ -5294,13 +5074,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920304</v>
+        <v>20330051920235</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -5311,13 +5091,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920305</v>
+        <v>21330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5328,13 +5108,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920307</v>
+        <v>21330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -5345,13 +5125,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920308</v>
+        <v>21330051920309</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5362,13 +5142,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920309</v>
+        <v>21330051920090</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5379,13 +5159,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920090</v>
+        <v>21330051920310</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5396,13 +5176,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920310</v>
+        <v>21330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>167</v>
@@ -5413,13 +5193,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920311</v>
+        <v>21330051920312</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5430,13 +5210,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920312</v>
+        <v>21330051920313</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5447,13 +5227,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920313</v>
+        <v>21330051920314</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5464,13 +5244,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920314</v>
+        <v>21330051920172</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5481,13 +5261,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920172</v>
+        <v>21330051920315</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5498,16 +5278,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920315</v>
+        <v>21330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5515,16 +5295,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920316</v>
+        <v>21330051920317</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5532,13 +5312,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920317</v>
+        <v>21330051920318</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -5549,13 +5329,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920318</v>
+        <v>21330051920319</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -5566,13 +5346,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920319</v>
+        <v>21330051920320</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -5583,13 +5363,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920320</v>
+        <v>21330051920321</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -5600,13 +5380,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920321</v>
+        <v>21330051920323</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -5617,13 +5397,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920323</v>
+        <v>21330051920324</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -5634,13 +5414,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920324</v>
+        <v>21330051920326</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -5651,13 +5431,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920326</v>
+        <v>21330051920327</v>
       </c>
       <c r="B42" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -5668,13 +5448,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920327</v>
+        <v>21330051920328</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -5688,10 +5468,10 @@
         <v>21330051920329</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -5705,10 +5485,10 @@
         <v>21330051920330</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
@@ -5724,7 +5504,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5756,16 +5536,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920289</v>
+        <v>21330051920297</v>
       </c>
       <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5774,21 +5554,21 @@
         <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920289</v>
+        <v>21330051920297</v>
       </c>
       <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5797,21 +5577,21 @@
         <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920299</v>
+        <v>21330051920308</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5820,21 +5600,21 @@
         <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920299</v>
+        <v>21330051920308</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5843,44 +5623,44 @@
         <v>66</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920337</v>
+        <v>21330051920289</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920337</v>
+        <v>21330051920298</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5894,62 +5674,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920297</v>
+        <v>21330051920299</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920306</v>
+        <v>21330051920337</v>
       </c>
       <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920235</v>
+        <v>21330051920306</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5958,21 +5738,21 @@
         <v>65</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920328</v>
+        <v>20330051920235</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -5981,7 +5761,76 @@
         <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920312</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920328</v>
+      </c>
+      <c r="B14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="185">
   <si>
     <t>Materia</t>
   </si>
@@ -218,13 +218,13 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -1094,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1103,13 +1103,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -1121,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1171,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1180,16 +1180,16 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -1248,7 +1248,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1257,13 +1257,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1275,10 +1275,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1325,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1334,13 +1334,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1402,7 +1402,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1411,16 +1411,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1479,7 +1479,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1488,16 +1488,16 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1506,10 +1506,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1556,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1565,13 +1565,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1583,10 +1583,10 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1633,7 +1633,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1642,16 +1642,16 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1663,7 +1663,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1710,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1719,16 +1719,16 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1740,10 +1740,10 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1787,7 +1787,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1796,16 +1796,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1817,10 +1817,10 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1864,7 +1864,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1873,16 +1873,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1894,7 +1894,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1941,7 +1941,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1950,13 +1950,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -2018,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2027,13 +2027,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -2048,10 +2048,10 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2104,16 +2104,16 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -2172,7 +2172,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2181,16 +2181,16 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2249,7 +2249,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2258,13 +2258,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2326,7 +2326,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2335,16 +2335,16 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2353,10 +2353,10 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2403,7 +2403,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2412,16 +2412,16 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2430,13 +2430,13 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2480,7 +2480,7 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2489,16 +2489,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2510,10 +2510,10 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2566,16 +2566,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2584,13 +2584,13 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2634,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2643,16 +2643,16 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2661,7 +2661,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2711,7 +2711,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2720,13 +2720,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2744,7 +2744,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2788,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2797,16 +2797,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>9</v>
@@ -2815,10 +2815,10 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2874,13 +2874,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2895,10 +2895,10 @@
         <v>7</v>
       </c>
       <c r="X27">
+        <v>6</v>
+      </c>
+      <c r="Y27">
         <v>5</v>
-      </c>
-      <c r="Y27">
-        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2942,7 +2942,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2951,13 +2951,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2969,10 +2969,10 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3028,13 +3028,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3046,10 +3046,10 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3096,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3105,16 +3105,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3123,10 +3123,10 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3173,7 +3173,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3182,16 +3182,16 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3200,13 +3200,13 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3250,7 +3250,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3259,13 +3259,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3277,13 +3277,13 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3327,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3336,13 +3336,13 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3354,13 +3354,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3404,7 +3404,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3413,13 +3413,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3434,7 +3434,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3490,13 +3490,13 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3558,7 +3558,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3567,13 +3567,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3585,10 +3585,10 @@
         <v>10</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3635,7 +3635,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3644,16 +3644,16 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>9</v>
@@ -3662,7 +3662,7 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3712,7 +3712,7 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3721,16 +3721,16 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3742,10 +3742,10 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y38">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3789,7 +3789,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3798,13 +3798,13 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3819,7 +3819,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3866,7 +3866,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3875,16 +3875,16 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>8</v>
@@ -3893,7 +3893,7 @@
         <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3943,7 +3943,7 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3952,13 +3952,13 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>6</v>
@@ -4020,7 +4020,7 @@
         <v>9</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -4029,16 +4029,16 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U42">
         <v>8</v>
@@ -4053,7 +4053,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4097,7 +4097,7 @@
         <v>10</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>-1</v>
@@ -4106,16 +4106,16 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>10</v>
@@ -4127,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y43">
         <v>9</v>
@@ -4174,7 +4174,7 @@
         <v>7</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
         <v>-1</v>
@@ -4183,13 +4183,13 @@
         <v>-1</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>9</v>
@@ -4207,7 +4207,7 @@
         <v>9</v>
       </c>
       <c r="Y44">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4251,7 +4251,7 @@
         <v>8</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O45">
         <v>-1</v>
@@ -4260,16 +4260,16 @@
         <v>-1</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45">
         <v>7</v>
@@ -4278,10 +4278,10 @@
         <v>7</v>
       </c>
       <c r="W45">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X45">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y45">
         <v>7</v>
@@ -4328,7 +4328,7 @@
         <v>10</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>-1</v>
@@ -4337,13 +4337,13 @@
         <v>-1</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T46">
         <v>7</v>
@@ -4355,10 +4355,10 @@
         <v>9</v>
       </c>
       <c r="W46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y46">
         <v>9</v>
@@ -4405,7 +4405,7 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O47">
         <v>-1</v>
@@ -4414,13 +4414,13 @@
         <v>-1</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T47">
         <v>6</v>
@@ -4432,10 +4432,10 @@
         <v>10</v>
       </c>
       <c r="W47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y47">
         <v>9</v>
@@ -4503,19 +4503,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>86.36</v>
+        <v>97.73</v>
       </c>
       <c r="G2">
-        <v>13.64</v>
+        <v>2.27</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4535,16 +4535,16 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>88.64</v>
+        <v>97.73</v>
       </c>
       <c r="G3">
-        <v>11.36</v>
+        <v>2.27</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4567,19 +4567,19 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5504,7 +5504,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5536,16 +5536,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920297</v>
+        <v>21330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5559,277 +5559,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920297</v>
+        <v>21330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920308</v>
-      </c>
-      <c r="B4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920308</v>
-      </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920289</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920298</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920299</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920306</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920235</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920311</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920312</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920328</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" t="s">
-        <v>182</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BLCM - Estadisticos 20212.xlsx
+++ b/grupos/2BLCM - Estadisticos 20212.xlsx
@@ -1097,10 +1097,10 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -1159,7 +1159,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -1174,10 +1174,10 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -1192,7 +1192,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1251,10 +1251,10 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>8</v>
@@ -1328,10 +1328,10 @@
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1405,10 +1405,10 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1423,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1482,10 +1482,10 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1500,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1559,10 +1559,10 @@
         <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1577,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1636,10 +1636,10 @@
         <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1654,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1713,10 +1713,10 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1731,7 +1731,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1790,10 +1790,10 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1808,7 +1808,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1867,10 +1867,10 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -1944,10 +1944,10 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1962,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -2021,10 +2021,10 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -2098,10 +2098,10 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -2116,7 +2116,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2175,10 +2175,10 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2252,10 +2252,10 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2270,7 +2270,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2329,10 +2329,10 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2406,10 +2406,10 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2483,10 +2483,10 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>8</v>
@@ -2560,10 +2560,10 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2637,10 +2637,10 @@
         <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2714,10 +2714,10 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -2791,10 +2791,10 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2868,10 +2868,10 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>8</v>
@@ -2945,10 +2945,10 @@
         <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>5</v>
@@ -3022,10 +3022,10 @@
         <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>6</v>
@@ -3040,7 +3040,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3099,10 +3099,10 @@
         <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -3176,10 +3176,10 @@
         <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3194,7 +3194,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3253,10 +3253,10 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>8</v>
@@ -3330,10 +3330,10 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>7</v>
@@ -3407,10 +3407,10 @@
         <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3484,10 +3484,10 @@
         <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>9</v>
@@ -3561,10 +3561,10 @@
         <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>8</v>
@@ -3638,10 +3638,10 @@
         <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -3715,10 +3715,10 @@
         <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>8</v>
@@ -3733,7 +3733,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3792,10 +3792,10 @@
         <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>9</v>
@@ -3869,10 +3869,10 @@
         <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>8</v>
@@ -3946,10 +3946,10 @@
         <v>6</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>10</v>
@@ -3964,7 +3964,7 @@
         <v>6</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -4023,10 +4023,10 @@
         <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4100,10 +4100,10 @@
         <v>6</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
         <v>9</v>
@@ -4118,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V43">
         <v>10</v>
@@ -4177,10 +4177,10 @@
         <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
         <v>10</v>
@@ -4239,7 +4239,7 @@
         <v>7</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K45">
         <v>9</v>
@@ -4254,10 +4254,10 @@
         <v>8</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q45">
         <v>8</v>
@@ -4331,10 +4331,10 @@
         <v>6</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q46">
         <v>9</v>
@@ -4393,7 +4393,7 @@
         <v>7</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K47">
         <v>8</v>
@@ -4408,10 +4408,10 @@
         <v>6</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q47">
         <v>8</v>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
